--- a/data/output/cleaned/cleaned_data.xlsx
+++ b/data/output/cleaned/cleaned_data.xlsx
@@ -28886,8 +28886,10 @@
     <row r="413"/>
     <row r="414"/>
     <row r="415">
-      <c r="I415" t="n">
-        <v>574</v>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/output/cleaned/cleaned_data.xlsx
+++ b/data/output/cleaned/cleaned_data.xlsx
@@ -542,7 +542,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46056</v>
+        <v>46083</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -601,8 +601,10 @@
       <c r="N2" t="n">
         <v>1661991</v>
       </c>
-      <c r="O2" t="n">
-        <v>792602652</v>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>792602652.0</t>
+        </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -612,7 +614,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>46058</v>
+        <v>46144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -666,8 +668,10 @@
       <c r="N3" t="n">
         <v>5745801</v>
       </c>
-      <c r="O3" t="n">
-        <v>792602653</v>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>792602653.0</t>
+        </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -677,7 +681,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46058</v>
+        <v>46144</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -736,8 +740,10 @@
       <c r="N4" t="n">
         <v>5745802</v>
       </c>
-      <c r="O4" t="n">
-        <v>792602654</v>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>792602654.0</t>
+        </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -747,7 +753,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46060</v>
+        <v>46205</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -806,8 +812,10 @@
       <c r="N5" t="n">
         <v>5745803</v>
       </c>
-      <c r="O5" t="n">
-        <v>792602655</v>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>792602655.0</t>
+        </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -817,7 +825,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -876,8 +884,10 @@
       <c r="N6" t="n">
         <v>5745804</v>
       </c>
-      <c r="O6" t="n">
-        <v>792602656</v>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>792602656.0</t>
+        </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -887,7 +897,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46057</v>
+        <v>46114</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -946,8 +956,10 @@
       <c r="N7" t="n">
         <v>5745805</v>
       </c>
-      <c r="O7" t="n">
-        <v>792602657</v>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>792602657.0</t>
+        </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -957,7 +969,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46061</v>
+        <v>46236</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1016,8 +1028,10 @@
       <c r="N8" t="n">
         <v>5745806</v>
       </c>
-      <c r="O8" t="n">
-        <v>792602658</v>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>792602658.0</t>
+        </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1027,7 +1041,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46063</v>
+        <v>46297</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1086,8 +1100,10 @@
       <c r="N9" t="n">
         <v>5745807</v>
       </c>
-      <c r="O9" t="n">
-        <v>792602659</v>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>792602659.0</t>
+        </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1097,7 +1113,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46062</v>
+        <v>46267</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1156,8 +1172,10 @@
       <c r="N10" t="n">
         <v>5745808</v>
       </c>
-      <c r="O10" t="n">
-        <v>792602660</v>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>792602660.0</t>
+        </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1167,7 +1185,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46063</v>
+        <v>46297</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1226,8 +1244,10 @@
       <c r="N11" t="n">
         <v>5745809</v>
       </c>
-      <c r="O11" t="n">
-        <v>792602661</v>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>792602661.0</t>
+        </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1237,7 +1257,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46063</v>
+        <v>46297</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1296,8 +1316,10 @@
       <c r="N12" t="n">
         <v>5745810</v>
       </c>
-      <c r="O12" t="n">
-        <v>792602662</v>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>792602662.0</t>
+        </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1307,7 +1329,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46065</v>
+        <v>46358</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1366,8 +1388,10 @@
       <c r="N13" t="n">
         <v>5745811</v>
       </c>
-      <c r="O13" t="n">
-        <v>792602663</v>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>792602663.0</t>
+        </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1377,7 +1401,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46065</v>
+        <v>46358</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1436,8 +1460,10 @@
       <c r="N14" t="n">
         <v>5745812</v>
       </c>
-      <c r="O14" t="n">
-        <v>792602664</v>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>792602664.0</t>
+        </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1447,7 +1473,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46065</v>
+        <v>46358</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1506,8 +1532,10 @@
       <c r="N15" t="n">
         <v>5745813</v>
       </c>
-      <c r="O15" t="n">
-        <v>792602665</v>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>792602665.0</t>
+        </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1576,8 +1604,10 @@
       <c r="N16" t="n">
         <v>5745814</v>
       </c>
-      <c r="O16" t="n">
-        <v>792602666</v>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>792602666.0</t>
+        </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1646,8 +1676,10 @@
       <c r="N17" t="n">
         <v>5745815</v>
       </c>
-      <c r="O17" t="n">
-        <v>792602667</v>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>792602667.0</t>
+        </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1716,8 +1748,10 @@
       <c r="N18" t="n">
         <v>5745816</v>
       </c>
-      <c r="O18" t="n">
-        <v>792602668</v>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>792602668.0</t>
+        </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -1786,8 +1820,10 @@
       <c r="N19" t="n">
         <v>5745817</v>
       </c>
-      <c r="O19" t="n">
-        <v>792602669</v>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>792602669.0</t>
+        </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -1856,8 +1892,10 @@
       <c r="N20" t="n">
         <v>5745818</v>
       </c>
-      <c r="O20" t="n">
-        <v>792602670</v>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>792602670.0</t>
+        </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -1926,8 +1964,10 @@
       <c r="N21" t="n">
         <v>5745819</v>
       </c>
-      <c r="O21" t="n">
-        <v>792602671</v>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>792602671.0</t>
+        </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1996,8 +2036,10 @@
       <c r="N22" t="n">
         <v>5745820</v>
       </c>
-      <c r="O22" t="n">
-        <v>792602672</v>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>792602672.0</t>
+        </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2066,8 +2108,10 @@
       <c r="N23" t="n">
         <v>5745821</v>
       </c>
-      <c r="O23" t="n">
-        <v>792602673</v>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>792602673.0</t>
+        </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2136,8 +2180,10 @@
       <c r="N24" t="n">
         <v>5745822</v>
       </c>
-      <c r="O24" t="n">
-        <v>792602674</v>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>792602674.0</t>
+        </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2206,8 +2252,10 @@
       <c r="N25" t="n">
         <v>5745823</v>
       </c>
-      <c r="O25" t="n">
-        <v>792602675</v>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>792602675.0</t>
+        </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2276,8 +2324,10 @@
       <c r="N26" t="n">
         <v>5745824</v>
       </c>
-      <c r="O26" t="n">
-        <v>792602676</v>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>792602676.0</t>
+        </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2346,8 +2396,10 @@
       <c r="N27" t="n">
         <v>5745825</v>
       </c>
-      <c r="O27" t="n">
-        <v>792602677</v>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>792602677.0</t>
+        </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2416,8 +2468,10 @@
       <c r="N28" t="n">
         <v>5745826</v>
       </c>
-      <c r="O28" t="n">
-        <v>792602678</v>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>792602678.0</t>
+        </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2486,8 +2540,10 @@
       <c r="N29" t="n">
         <v>5745827</v>
       </c>
-      <c r="O29" t="n">
-        <v>792602679</v>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>792602679.0</t>
+        </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -2556,8 +2612,10 @@
       <c r="N30" t="n">
         <v>5745828</v>
       </c>
-      <c r="O30" t="n">
-        <v>792602680</v>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>792602680.0</t>
+        </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -2626,8 +2684,10 @@
       <c r="N31" t="n">
         <v>5745829</v>
       </c>
-      <c r="O31" t="n">
-        <v>792602681</v>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>792602681.0</t>
+        </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -2637,7 +2697,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46082</v>
+        <v>46025</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2696,8 +2756,10 @@
       <c r="N32" t="n">
         <v>5745830</v>
       </c>
-      <c r="O32" t="n">
-        <v>792602682</v>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>792602682.0</t>
+        </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -2707,7 +2769,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46082</v>
+        <v>46025</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2766,8 +2828,10 @@
       <c r="N33" t="n">
         <v>5745831</v>
       </c>
-      <c r="O33" t="n">
-        <v>792602683</v>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>792602683.0</t>
+        </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -2836,8 +2900,10 @@
       <c r="N34" t="n">
         <v>5745832</v>
       </c>
-      <c r="O34" t="n">
-        <v>792602684</v>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>792602684.0</t>
+        </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -2906,8 +2972,10 @@
       <c r="N35" t="n">
         <v>5745834</v>
       </c>
-      <c r="O35" t="n">
-        <v>792602685</v>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>792602685.0</t>
+        </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -2976,8 +3044,10 @@
       <c r="N36" t="n">
         <v>5745835</v>
       </c>
-      <c r="O36" t="n">
-        <v>792602686</v>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>792602686.0</t>
+        </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -2987,7 +3057,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46083</v>
+        <v>46056</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3046,8 +3116,10 @@
       <c r="N37" t="n">
         <v>5745836</v>
       </c>
-      <c r="O37" t="n">
-        <v>792602687</v>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>792602687.0</t>
+        </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -3057,7 +3129,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46082</v>
+        <v>46025</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3116,8 +3188,10 @@
       <c r="N38" t="n">
         <v>5745837</v>
       </c>
-      <c r="O38" t="n">
-        <v>792602688</v>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>792602688.0</t>
+        </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -3127,7 +3201,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46083</v>
+        <v>46056</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3186,8 +3260,10 @@
       <c r="N39" t="n">
         <v>5745838</v>
       </c>
-      <c r="O39" t="n">
-        <v>792602689</v>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>792602689.0</t>
+        </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -3256,8 +3332,10 @@
       <c r="N40" t="n">
         <v>5745839</v>
       </c>
-      <c r="O40" t="n">
-        <v>792602690</v>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>792602690.0</t>
+        </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -3267,7 +3345,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46083</v>
+        <v>46056</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3326,8 +3404,10 @@
       <c r="N41" t="n">
         <v>5745840</v>
       </c>
-      <c r="O41" t="n">
-        <v>792602691</v>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>792602691.0</t>
+        </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -3337,7 +3417,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46086</v>
+        <v>46145</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3396,8 +3476,10 @@
       <c r="N42" t="n">
         <v>5745841</v>
       </c>
-      <c r="O42" t="n">
-        <v>792602692</v>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>792602692.0</t>
+        </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -3407,7 +3489,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46087</v>
+        <v>46176</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3466,8 +3548,10 @@
       <c r="N43" t="n">
         <v>5745842</v>
       </c>
-      <c r="O43" t="n">
-        <v>792602693</v>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>792602693.0</t>
+        </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -3477,7 +3561,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46087</v>
+        <v>46176</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3536,8 +3620,10 @@
       <c r="N44" t="n">
         <v>5745843</v>
       </c>
-      <c r="O44" t="n">
-        <v>792602694</v>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>792602694.0</t>
+        </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -3547,7 +3633,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46087</v>
+        <v>46176</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3606,8 +3692,10 @@
       <c r="N45" t="n">
         <v>5745844</v>
       </c>
-      <c r="O45" t="n">
-        <v>792602695</v>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>792602695.0</t>
+        </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -3617,7 +3705,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46088</v>
+        <v>46206</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3676,8 +3764,10 @@
       <c r="N46" t="n">
         <v>5745845</v>
       </c>
-      <c r="O46" t="n">
-        <v>792602696</v>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>792602696.0</t>
+        </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -3687,7 +3777,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46091</v>
+        <v>46298</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3746,8 +3836,10 @@
       <c r="N47" t="n">
         <v>5745846</v>
       </c>
-      <c r="O47" t="n">
-        <v>792602697</v>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>792602697.0</t>
+        </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -3816,8 +3908,10 @@
       <c r="N48" t="n">
         <v>5786951</v>
       </c>
-      <c r="O48" t="n">
-        <v>792602698</v>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>792602698.0</t>
+        </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -3886,8 +3980,10 @@
       <c r="N49" t="n">
         <v>5786952</v>
       </c>
-      <c r="O49" t="n">
-        <v>792602699</v>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>792602699.0</t>
+        </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -3956,8 +4052,10 @@
       <c r="N50" t="n">
         <v>5786953</v>
       </c>
-      <c r="O50" t="n">
-        <v>792602700</v>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>792602700.0</t>
+        </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -4026,8 +4124,10 @@
       <c r="N51" t="n">
         <v>5786954</v>
       </c>
-      <c r="O51" t="n">
-        <v>792602701</v>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>792602701.0</t>
+        </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -4096,8 +4196,10 @@
       <c r="N52" t="n">
         <v>5786955</v>
       </c>
-      <c r="O52" t="n">
-        <v>792602702</v>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>792602702.0</t>
+        </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -4166,8 +4268,10 @@
       <c r="N53" t="n">
         <v>5786956</v>
       </c>
-      <c r="O53" t="n">
-        <v>792602703</v>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>792602703.0</t>
+        </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -4236,8 +4340,10 @@
       <c r="N54" t="n">
         <v>5786957</v>
       </c>
-      <c r="O54" t="n">
-        <v>792602704</v>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>792602704.0</t>
+        </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -4306,8 +4412,10 @@
       <c r="N55" t="n">
         <v>5786958</v>
       </c>
-      <c r="O55" t="n">
-        <v>792602705</v>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>792602705.0</t>
+        </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -4376,8 +4484,10 @@
       <c r="N56" t="n">
         <v>5786959</v>
       </c>
-      <c r="O56" t="n">
-        <v>792602706</v>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>792602706.0</t>
+        </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -4446,8 +4556,10 @@
       <c r="N57" t="n">
         <v>5786960</v>
       </c>
-      <c r="O57" t="n">
-        <v>792602707</v>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>792602707.0</t>
+        </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -4516,8 +4628,10 @@
       <c r="N58" t="n">
         <v>5786961</v>
       </c>
-      <c r="O58" t="n">
-        <v>792602708</v>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>792602708.0</t>
+        </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -4586,8 +4700,10 @@
       <c r="N59" t="n">
         <v>5786962</v>
       </c>
-      <c r="O59" t="n">
-        <v>792602709</v>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>792602709.0</t>
+        </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -4597,7 +4713,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46024</v>
+        <v>46054</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -4656,8 +4772,10 @@
       <c r="N60" t="n">
         <v>5786963</v>
       </c>
-      <c r="O60" t="n">
-        <v>792602710</v>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>792602710.0</t>
+        </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -4667,7 +4785,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46028</v>
+        <v>46174</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -4726,8 +4844,10 @@
       <c r="N61" t="n">
         <v>5786964</v>
       </c>
-      <c r="O61" t="n">
-        <v>792602711</v>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>792602711.0</t>
+        </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -4796,8 +4916,10 @@
       <c r="N62" t="n">
         <v>5786965</v>
       </c>
-      <c r="O62" t="n">
-        <v>792602712</v>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>792602712.0</t>
+        </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -4866,8 +4988,10 @@
       <c r="N63" t="n">
         <v>5786966</v>
       </c>
-      <c r="O63" t="n">
-        <v>792602713</v>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>792602713.0</t>
+        </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -4936,8 +5060,10 @@
       <c r="N64" t="n">
         <v>5786967</v>
       </c>
-      <c r="O64" t="n">
-        <v>792602714</v>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>792602714.0</t>
+        </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -5006,8 +5132,10 @@
       <c r="N65" t="n">
         <v>5786968</v>
       </c>
-      <c r="O65" t="n">
-        <v>792602715</v>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>792602715.0</t>
+        </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -5076,8 +5204,10 @@
       <c r="N66" t="n">
         <v>5786969</v>
       </c>
-      <c r="O66" t="n">
-        <v>792602716</v>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>792602716.0</t>
+        </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -5146,8 +5276,10 @@
       <c r="N67" t="n">
         <v>5786970</v>
       </c>
-      <c r="O67" t="n">
-        <v>792602717</v>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>792602717.0</t>
+        </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -5216,8 +5348,10 @@
       <c r="N68" t="n">
         <v>5786972</v>
       </c>
-      <c r="O68" t="n">
-        <v>792602718</v>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>792602718.0</t>
+        </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -5286,8 +5420,10 @@
       <c r="N69" t="n">
         <v>5786973</v>
       </c>
-      <c r="O69" t="n">
-        <v>792602719</v>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>792602719.0</t>
+        </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -5297,7 +5433,7 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46025</v>
+        <v>46082</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -5356,8 +5492,10 @@
       <c r="N70" t="n">
         <v>5786974</v>
       </c>
-      <c r="O70" t="n">
-        <v>792602720</v>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>792602720.0</t>
+        </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -5367,7 +5505,7 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46025</v>
+        <v>46082</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5426,8 +5564,10 @@
       <c r="N71" t="n">
         <v>5786975</v>
       </c>
-      <c r="O71" t="n">
-        <v>792602721</v>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>792602721.0</t>
+        </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -5437,7 +5577,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46027</v>
+        <v>46143</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -5496,8 +5636,10 @@
       <c r="N72" t="n">
         <v>5786976</v>
       </c>
-      <c r="O72" t="n">
-        <v>792602722</v>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>792602722.0</t>
+        </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
@@ -5507,7 +5649,7 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46034</v>
+        <v>46357</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -5566,8 +5708,10 @@
       <c r="N73" t="n">
         <v>5786978</v>
       </c>
-      <c r="O73" t="n">
-        <v>792602723</v>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>792602723.0</t>
+        </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -5636,8 +5780,10 @@
       <c r="N74" t="n">
         <v>5786979</v>
       </c>
-      <c r="O74" t="n">
-        <v>792602724</v>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>792602724.0</t>
+        </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -5706,8 +5852,10 @@
       <c r="N75" t="n">
         <v>5786980</v>
       </c>
-      <c r="O75" t="n">
-        <v>792602725</v>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>792602725.0</t>
+        </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -5776,8 +5924,10 @@
       <c r="N76" t="n">
         <v>5786981</v>
       </c>
-      <c r="O76" t="n">
-        <v>792602726</v>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>792602726.0</t>
+        </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -5846,8 +5996,10 @@
       <c r="N77" t="n">
         <v>5786982</v>
       </c>
-      <c r="O77" t="n">
-        <v>792602727</v>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>792602727.0</t>
+        </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -5857,7 +6009,7 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46058</v>
+        <v>46144</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -5916,8 +6068,10 @@
       <c r="N78" t="n">
         <v>5786983</v>
       </c>
-      <c r="O78" t="n">
-        <v>792602728</v>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>792602728.0</t>
+        </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
@@ -5927,7 +6081,7 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>45999</v>
+        <v>45881</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -5986,12 +6140,14 @@
       <c r="N79" t="n">
         <v>5786984</v>
       </c>
-      <c r="O79" t="n">
-        <v>792602729</v>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>792602729.0</t>
+        </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
@@ -6056,8 +6212,10 @@
       <c r="N80" t="n">
         <v>5786985</v>
       </c>
-      <c r="O80" t="n">
-        <v>792602730</v>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>792602730.0</t>
+        </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
@@ -6126,8 +6284,10 @@
       <c r="N81" t="n">
         <v>5786986</v>
       </c>
-      <c r="O81" t="n">
-        <v>792602731</v>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>792602731.0</t>
+        </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
@@ -6196,8 +6356,10 @@
       <c r="N82" t="n">
         <v>5786987</v>
       </c>
-      <c r="O82" t="n">
-        <v>792602732</v>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>792602732.0</t>
+        </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -6266,8 +6428,10 @@
       <c r="N83" t="n">
         <v>5786988</v>
       </c>
-      <c r="O83" t="n">
-        <v>792602733</v>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>792602733.0</t>
+        </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -6336,8 +6500,10 @@
       <c r="N84" t="n">
         <v>5786989</v>
       </c>
-      <c r="O84" t="n">
-        <v>792602734</v>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>792602734.0</t>
+        </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -6406,8 +6572,10 @@
       <c r="N85" t="n">
         <v>5786990</v>
       </c>
-      <c r="O85" t="n">
-        <v>792602735</v>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>792602735.0</t>
+        </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
@@ -6417,7 +6585,7 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46001</v>
+        <v>45942</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -6476,12 +6644,14 @@
       <c r="N86" t="n">
         <v>5786991</v>
       </c>
-      <c r="O86" t="n">
-        <v>792602736</v>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>792602736.0</t>
+        </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
@@ -6546,8 +6716,10 @@
       <c r="N87" t="n">
         <v>5786992</v>
       </c>
-      <c r="O87" t="n">
-        <v>792602737</v>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>792602737.0</t>
+        </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -6616,8 +6788,10 @@
       <c r="N88" t="n">
         <v>5786993</v>
       </c>
-      <c r="O88" t="n">
-        <v>792602738</v>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>792602738.0</t>
+        </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -6686,8 +6860,10 @@
       <c r="N89" t="n">
         <v>5786994</v>
       </c>
-      <c r="O89" t="n">
-        <v>792602739</v>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>792602739.0</t>
+        </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -6697,7 +6873,7 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46091</v>
+        <v>46298</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -6756,8 +6932,10 @@
       <c r="N90" t="n">
         <v>5745847</v>
       </c>
-      <c r="O90" t="n">
-        <v>792602740</v>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>792602740.0</t>
+        </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
@@ -6767,7 +6945,7 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46091</v>
+        <v>46298</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -6826,8 +7004,10 @@
       <c r="N91" t="n">
         <v>5745848</v>
       </c>
-      <c r="O91" t="n">
-        <v>792602741</v>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>792602741.0</t>
+        </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
@@ -6896,8 +7076,10 @@
       <c r="N92" t="n">
         <v>5550951</v>
       </c>
-      <c r="O92" t="n">
-        <v>792602742</v>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>792602742.0</t>
+        </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -6966,8 +7148,10 @@
       <c r="N93" t="n">
         <v>5634501</v>
       </c>
-      <c r="O93" t="n">
-        <v>792602743</v>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>792602743.0</t>
+        </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -7036,8 +7220,10 @@
       <c r="N94" t="n">
         <v>5634502</v>
       </c>
-      <c r="O94" t="n">
-        <v>792602744</v>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>792602744.0</t>
+        </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -7106,8 +7292,10 @@
       <c r="N95" t="n">
         <v>5634503</v>
       </c>
-      <c r="O95" t="n">
-        <v>792602745</v>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>792602745.0</t>
+        </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
@@ -7176,8 +7364,10 @@
       <c r="N96" t="n">
         <v>5634504</v>
       </c>
-      <c r="O96" t="n">
-        <v>792602746</v>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>792602746.0</t>
+        </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
@@ -7246,8 +7436,10 @@
       <c r="N97" t="n">
         <v>5634505</v>
       </c>
-      <c r="O97" t="n">
-        <v>792602747</v>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>792602747.0</t>
+        </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -7316,8 +7508,10 @@
       <c r="N98" t="n">
         <v>5634506</v>
       </c>
-      <c r="O98" t="n">
-        <v>792602748</v>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>792602748.0</t>
+        </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -7386,8 +7580,10 @@
       <c r="N99" t="n">
         <v>5634507</v>
       </c>
-      <c r="O99" t="n">
-        <v>792602749</v>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>792602749.0</t>
+        </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -7456,8 +7652,10 @@
       <c r="N100" t="n">
         <v>5634508</v>
       </c>
-      <c r="O100" t="n">
-        <v>792602750</v>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>792602750.0</t>
+        </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -7526,8 +7724,10 @@
       <c r="N101" t="n">
         <v>5634509</v>
       </c>
-      <c r="O101" t="n">
-        <v>792602751</v>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>792602751.0</t>
+        </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -7596,8 +7796,10 @@
       <c r="N102" t="n">
         <v>5634510</v>
       </c>
-      <c r="O102" t="n">
-        <v>792602752</v>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>792602752.0</t>
+        </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
@@ -7666,8 +7868,10 @@
       <c r="N103" t="n">
         <v>5634511</v>
       </c>
-      <c r="O103" t="n">
-        <v>792602753</v>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>792602753.0</t>
+        </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
@@ -7736,8 +7940,10 @@
       <c r="N104" t="n">
         <v>5634512</v>
       </c>
-      <c r="O104" t="n">
-        <v>792602754</v>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>792602754.0</t>
+        </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -7806,8 +8012,10 @@
       <c r="N105" t="n">
         <v>5634513</v>
       </c>
-      <c r="O105" t="n">
-        <v>792602755</v>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>792602755.0</t>
+        </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -7876,8 +8084,10 @@
       <c r="N106" t="n">
         <v>5634514</v>
       </c>
-      <c r="O106" t="n">
-        <v>792602756</v>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>792602756.0</t>
+        </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
@@ -7946,8 +8156,10 @@
       <c r="N107" t="n">
         <v>5634515</v>
       </c>
-      <c r="O107" t="n">
-        <v>792602757</v>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>792602757.0</t>
+        </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -8016,8 +8228,10 @@
       <c r="N108" t="n">
         <v>5634516</v>
       </c>
-      <c r="O108" t="n">
-        <v>792602758</v>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>792602758.0</t>
+        </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -8086,8 +8300,10 @@
       <c r="N109" t="n">
         <v>5634517</v>
       </c>
-      <c r="O109" t="n">
-        <v>792602759</v>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>792602759.0</t>
+        </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -8156,8 +8372,10 @@
       <c r="N110" t="n">
         <v>5634518</v>
       </c>
-      <c r="O110" t="n">
-        <v>792602760</v>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>792602760.0</t>
+        </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -8226,8 +8444,10 @@
       <c r="N111" t="n">
         <v>5634519</v>
       </c>
-      <c r="O111" t="n">
-        <v>792602761</v>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>792602761.0</t>
+        </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -8296,8 +8516,10 @@
       <c r="N112" t="n">
         <v>5634520</v>
       </c>
-      <c r="O112" t="n">
-        <v>792602762</v>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>792602762.0</t>
+        </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -8366,8 +8588,10 @@
       <c r="N113" t="n">
         <v>5634521</v>
       </c>
-      <c r="O113" t="n">
-        <v>792602763</v>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>792602763.0</t>
+        </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -8436,8 +8660,10 @@
       <c r="N114" t="n">
         <v>5634522</v>
       </c>
-      <c r="O114" t="n">
-        <v>792602764</v>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>792602764.0</t>
+        </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -8506,8 +8732,10 @@
       <c r="N115" t="n">
         <v>5634523</v>
       </c>
-      <c r="O115" t="n">
-        <v>792602765</v>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>792602765.0</t>
+        </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -8576,8 +8804,10 @@
       <c r="N116" t="n">
         <v>5634524</v>
       </c>
-      <c r="O116" t="n">
-        <v>792602766</v>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>792602766.0</t>
+        </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
@@ -8646,8 +8876,10 @@
       <c r="N117" t="n">
         <v>5634525</v>
       </c>
-      <c r="O117" t="n">
-        <v>792602767</v>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>792602767.0</t>
+        </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -8716,8 +8948,10 @@
       <c r="N118" t="n">
         <v>5634526</v>
       </c>
-      <c r="O118" t="n">
-        <v>792602768</v>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>792602768.0</t>
+        </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
@@ -8786,8 +9020,10 @@
       <c r="N119" t="n">
         <v>5634527</v>
       </c>
-      <c r="O119" t="n">
-        <v>792602769</v>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>792602769.0</t>
+        </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
@@ -8856,8 +9092,10 @@
       <c r="N120" t="n">
         <v>5634528</v>
       </c>
-      <c r="O120" t="n">
-        <v>792602770</v>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>792602770.0</t>
+        </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
@@ -8926,8 +9164,10 @@
       <c r="N121" t="n">
         <v>5634529</v>
       </c>
-      <c r="O121" t="n">
-        <v>792602771</v>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>792602771.0</t>
+        </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
@@ -8996,8 +9236,10 @@
       <c r="N122" t="n">
         <v>5634530</v>
       </c>
-      <c r="O122" t="n">
-        <v>792602772</v>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>792602772.0</t>
+        </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -9066,8 +9308,10 @@
       <c r="N123" t="n">
         <v>5634531</v>
       </c>
-      <c r="O123" t="n">
-        <v>792602773</v>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>792602773.0</t>
+        </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -9136,8 +9380,10 @@
       <c r="N124" t="n">
         <v>5634532</v>
       </c>
-      <c r="O124" t="n">
-        <v>792602774</v>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>792602774.0</t>
+        </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -9206,8 +9452,10 @@
       <c r="N125" t="n">
         <v>5634533</v>
       </c>
-      <c r="O125" t="n">
-        <v>792602775</v>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>792602775.0</t>
+        </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
@@ -9276,8 +9524,10 @@
       <c r="N126" t="n">
         <v>5634534</v>
       </c>
-      <c r="O126" t="n">
-        <v>792602776</v>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>792602776.0</t>
+        </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
@@ -9346,8 +9596,10 @@
       <c r="N127" t="n">
         <v>5634535</v>
       </c>
-      <c r="O127" t="n">
-        <v>792602777</v>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>792602777.0</t>
+        </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
@@ -9416,8 +9668,10 @@
       <c r="N128" t="n">
         <v>5634536</v>
       </c>
-      <c r="O128" t="n">
-        <v>792602778</v>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>792602778.0</t>
+        </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -9486,8 +9740,10 @@
       <c r="N129" t="n">
         <v>5634537</v>
       </c>
-      <c r="O129" t="n">
-        <v>792602779</v>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>792602779.0</t>
+        </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -9556,8 +9812,10 @@
       <c r="N130" t="n">
         <v>5634538</v>
       </c>
-      <c r="O130" t="n">
-        <v>792602780</v>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>792602780.0</t>
+        </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
@@ -9626,8 +9884,10 @@
       <c r="N131" t="n">
         <v>5634539</v>
       </c>
-      <c r="O131" t="n">
-        <v>792602781</v>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>792602781.0</t>
+        </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -9696,8 +9956,10 @@
       <c r="N132" t="n">
         <v>5634540</v>
       </c>
-      <c r="O132" t="n">
-        <v>792602782</v>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>792602782.0</t>
+        </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
@@ -9766,8 +10028,10 @@
       <c r="N133" t="n">
         <v>5634541</v>
       </c>
-      <c r="O133" t="n">
-        <v>792602783</v>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>792602783.0</t>
+        </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -9836,8 +10100,10 @@
       <c r="N134" t="n">
         <v>5634542</v>
       </c>
-      <c r="O134" t="n">
-        <v>792602784</v>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>792602784.0</t>
+        </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
@@ -9906,8 +10172,10 @@
       <c r="N135" t="n">
         <v>5634543</v>
       </c>
-      <c r="O135" t="n">
-        <v>792602785</v>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>792602785.0</t>
+        </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
@@ -9976,8 +10244,10 @@
       <c r="N136" t="n">
         <v>5634544</v>
       </c>
-      <c r="O136" t="n">
-        <v>792602786</v>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>792602786.0</t>
+        </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
@@ -10046,8 +10316,10 @@
       <c r="N137" t="n">
         <v>5634545</v>
       </c>
-      <c r="O137" t="n">
-        <v>792602787</v>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>792602787.0</t>
+        </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
@@ -10116,8 +10388,10 @@
       <c r="N138" t="n">
         <v>5634546</v>
       </c>
-      <c r="O138" t="n">
-        <v>792602788</v>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>792602788.0</t>
+        </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
@@ -10186,8 +10460,10 @@
       <c r="N139" t="n">
         <v>5634547</v>
       </c>
-      <c r="O139" t="n">
-        <v>792602789</v>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>792602789.0</t>
+        </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
@@ -10256,8 +10532,10 @@
       <c r="N140" t="n">
         <v>5634548</v>
       </c>
-      <c r="O140" t="n">
-        <v>792602790</v>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>792602790.0</t>
+        </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
@@ -10326,8 +10604,10 @@
       <c r="N141" t="n">
         <v>5634549</v>
       </c>
-      <c r="O141" t="n">
-        <v>792602791</v>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>792602791.0</t>
+        </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
@@ -10396,8 +10676,10 @@
       <c r="N142" t="n">
         <v>5634550</v>
       </c>
-      <c r="O142" t="n">
-        <v>792602792</v>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>792602792.0</t>
+        </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
@@ -10466,8 +10748,10 @@
       <c r="N143" t="n">
         <v>5855501</v>
       </c>
-      <c r="O143" t="n">
-        <v>792602793</v>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>792602793.0</t>
+        </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
@@ -10536,8 +10820,10 @@
       <c r="N144" t="n">
         <v>5855502</v>
       </c>
-      <c r="O144" t="n">
-        <v>792602794</v>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>792602794.0</t>
+        </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
@@ -10606,8 +10892,10 @@
       <c r="N145" t="n">
         <v>5855503</v>
       </c>
-      <c r="O145" t="n">
-        <v>792602795</v>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>792602795.0</t>
+        </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
@@ -10676,8 +10964,10 @@
       <c r="N146" t="n">
         <v>5855504</v>
       </c>
-      <c r="O146" t="n">
-        <v>792602796</v>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>792602796.0</t>
+        </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
@@ -10746,8 +11036,10 @@
       <c r="N147" t="n">
         <v>5855505</v>
       </c>
-      <c r="O147" t="n">
-        <v>792602797</v>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>792602797.0</t>
+        </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
@@ -10816,8 +11108,10 @@
       <c r="N148" t="n">
         <v>5855506</v>
       </c>
-      <c r="O148" t="n">
-        <v>792602798</v>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>792602798.0</t>
+        </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -10886,8 +11180,10 @@
       <c r="N149" t="n">
         <v>5855507</v>
       </c>
-      <c r="O149" t="n">
-        <v>792602799</v>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>792602799.0</t>
+        </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
@@ -10956,8 +11252,10 @@
       <c r="N150" t="n">
         <v>5855508</v>
       </c>
-      <c r="O150" t="n">
-        <v>792602800</v>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>792602800.0</t>
+        </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
@@ -10967,7 +11265,7 @@
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46113</v>
+        <v>46026</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -11026,8 +11324,10 @@
       <c r="N151" t="n">
         <v>5855509</v>
       </c>
-      <c r="O151" t="n">
-        <v>792602801</v>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>792602801.0</t>
+        </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
@@ -11096,8 +11396,10 @@
       <c r="N152" t="n">
         <v>5855510</v>
       </c>
-      <c r="O152" t="n">
-        <v>792602802</v>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>792602802.0</t>
+        </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
@@ -11166,8 +11468,10 @@
       <c r="N153" t="n">
         <v>5855511</v>
       </c>
-      <c r="O153" t="n">
-        <v>792602803</v>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>792602803.0</t>
+        </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
@@ -11236,8 +11540,10 @@
       <c r="N154" t="n">
         <v>5855512</v>
       </c>
-      <c r="O154" t="n">
-        <v>792602804</v>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>792602804.0</t>
+        </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
@@ -11247,7 +11553,7 @@
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46113</v>
+        <v>46026</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -11306,8 +11612,10 @@
       <c r="N155" t="n">
         <v>5855513</v>
       </c>
-      <c r="O155" t="n">
-        <v>792602805</v>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>792602805.0</t>
+        </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
@@ -11317,7 +11625,7 @@
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46113</v>
+        <v>46026</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -11376,8 +11684,10 @@
       <c r="N156" t="n">
         <v>5855514</v>
       </c>
-      <c r="O156" t="n">
-        <v>792602806</v>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>792602806.0</t>
+        </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
@@ -11387,7 +11697,7 @@
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46113</v>
+        <v>46026</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -11446,8 +11756,10 @@
       <c r="N157" t="n">
         <v>5855515</v>
       </c>
-      <c r="O157" t="n">
-        <v>792602807</v>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>792602807.0</t>
+        </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
@@ -11457,7 +11769,7 @@
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -11516,8 +11828,10 @@
       <c r="N158" t="n">
         <v>5855516</v>
       </c>
-      <c r="O158" t="n">
-        <v>792602808</v>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>792602808.0</t>
+        </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
@@ -11527,7 +11841,7 @@
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46115</v>
+        <v>46085</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -11586,8 +11900,10 @@
       <c r="N159" t="n">
         <v>5855517</v>
       </c>
-      <c r="O159" t="n">
-        <v>792602809</v>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>792602809.0</t>
+        </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
@@ -11656,8 +11972,10 @@
       <c r="N160" t="n">
         <v>5855518</v>
       </c>
-      <c r="O160" t="n">
-        <v>792602810</v>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>792602810.0</t>
+        </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
@@ -11667,7 +11985,7 @@
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46113</v>
+        <v>46026</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -11726,8 +12044,10 @@
       <c r="N161" t="n">
         <v>5855519</v>
       </c>
-      <c r="O161" t="n">
-        <v>792602811</v>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>792602811.0</t>
+        </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
@@ -11737,7 +12057,7 @@
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -11796,8 +12116,10 @@
       <c r="N162" t="n">
         <v>5855520</v>
       </c>
-      <c r="O162" t="n">
-        <v>792602812</v>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>792602812.0</t>
+        </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
@@ -11807,7 +12129,7 @@
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46113</v>
+        <v>46026</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -11866,8 +12188,10 @@
       <c r="N163" t="n">
         <v>5855521</v>
       </c>
-      <c r="O163" t="n">
-        <v>792602813</v>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>792602813.0</t>
+        </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
@@ -11877,7 +12201,7 @@
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46113</v>
+        <v>46026</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -11936,8 +12260,10 @@
       <c r="N164" t="n">
         <v>5855522</v>
       </c>
-      <c r="O164" t="n">
-        <v>792602814</v>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>792602814.0</t>
+        </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
@@ -11947,7 +12273,7 @@
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -12006,8 +12332,10 @@
       <c r="N165" t="n">
         <v>5855523</v>
       </c>
-      <c r="O165" t="n">
-        <v>792602815</v>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>792602815.0</t>
+        </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
@@ -12017,7 +12345,7 @@
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -12076,8 +12404,10 @@
       <c r="N166" t="n">
         <v>5855524</v>
       </c>
-      <c r="O166" t="n">
-        <v>792602816</v>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>792602816.0</t>
+        </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
@@ -12087,7 +12417,7 @@
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -12146,8 +12476,10 @@
       <c r="N167" t="n">
         <v>5855525</v>
       </c>
-      <c r="O167" t="n">
-        <v>792602817</v>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>792602817.0</t>
+        </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
@@ -12157,7 +12489,7 @@
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -12216,8 +12548,10 @@
       <c r="N168" t="n">
         <v>5855526</v>
       </c>
-      <c r="O168" t="n">
-        <v>792602818</v>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>792602818.0</t>
+        </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
@@ -12227,7 +12561,7 @@
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>46113</v>
+        <v>46026</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -12286,8 +12620,10 @@
       <c r="N169" t="n">
         <v>5855527</v>
       </c>
-      <c r="O169" t="n">
-        <v>792602819</v>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>792602819.0</t>
+        </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
@@ -12297,7 +12633,7 @@
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
-        <v>46115</v>
+        <v>46085</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -12356,8 +12692,10 @@
       <c r="N170" t="n">
         <v>5855528</v>
       </c>
-      <c r="O170" t="n">
-        <v>792602820</v>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>792602820.0</t>
+        </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
@@ -12367,7 +12705,7 @@
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -12426,8 +12764,10 @@
       <c r="N171" t="n">
         <v>5855529</v>
       </c>
-      <c r="O171" t="n">
-        <v>792602821</v>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>792602821.0</t>
+        </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
@@ -12437,7 +12777,7 @@
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -12496,8 +12836,10 @@
       <c r="N172" t="n">
         <v>5855530</v>
       </c>
-      <c r="O172" t="n">
-        <v>792602822</v>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>792602822.0</t>
+        </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
@@ -12507,7 +12849,7 @@
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -12566,8 +12908,10 @@
       <c r="N173" t="n">
         <v>5855531</v>
       </c>
-      <c r="O173" t="n">
-        <v>792602823</v>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>792602823.0</t>
+        </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
@@ -12636,8 +12980,10 @@
       <c r="N174" t="n">
         <v>5855532</v>
       </c>
-      <c r="O174" t="n">
-        <v>792602824</v>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>792602824.0</t>
+        </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
@@ -12647,7 +12993,7 @@
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
-        <v>46113</v>
+        <v>46026</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -12706,8 +13052,10 @@
       <c r="N175" t="n">
         <v>5855533</v>
       </c>
-      <c r="O175" t="n">
-        <v>792602825</v>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>792602825.0</t>
+        </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
@@ -12776,8 +13124,10 @@
       <c r="N176" t="n">
         <v>5855534</v>
       </c>
-      <c r="O176" t="n">
-        <v>792602826</v>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>792602826.0</t>
+        </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
@@ -12787,7 +13137,7 @@
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
-        <v>46113</v>
+        <v>46026</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -12846,8 +13196,10 @@
       <c r="N177" t="n">
         <v>5855535</v>
       </c>
-      <c r="O177" t="n">
-        <v>792602827</v>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>792602827.0</t>
+        </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
@@ -12916,8 +13268,10 @@
       <c r="N178" t="n">
         <v>5855536</v>
       </c>
-      <c r="O178" t="n">
-        <v>792602828</v>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>792602828.0</t>
+        </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
@@ -12927,7 +13281,7 @@
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
-        <v>46115</v>
+        <v>46085</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -12986,8 +13340,10 @@
       <c r="N179" t="n">
         <v>5855538</v>
       </c>
-      <c r="O179" t="n">
-        <v>792602829</v>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>792602829.0</t>
+        </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
@@ -13056,8 +13412,10 @@
       <c r="N180" t="n">
         <v>5855539</v>
       </c>
-      <c r="O180" t="n">
-        <v>792602830</v>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>792602830.0</t>
+        </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
@@ -13067,7 +13425,7 @@
     </row>
     <row r="181">
       <c r="A181" s="3" t="n">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -13126,8 +13484,10 @@
       <c r="N181" t="n">
         <v>5855540</v>
       </c>
-      <c r="O181" t="n">
-        <v>792602831</v>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>792602831.0</t>
+        </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
@@ -13137,7 +13497,7 @@
     </row>
     <row r="182">
       <c r="A182" s="3" t="n">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -13196,8 +13556,10 @@
       <c r="N182" t="n">
         <v>5855541</v>
       </c>
-      <c r="O182" t="n">
-        <v>792602832</v>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>792602832.0</t>
+        </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
@@ -13266,8 +13628,10 @@
       <c r="N183" t="n">
         <v>5855542</v>
       </c>
-      <c r="O183" t="n">
-        <v>792602833</v>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>792602833.0</t>
+        </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
@@ -13277,7 +13641,7 @@
     </row>
     <row r="184">
       <c r="A184" s="3" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -13336,8 +13700,10 @@
       <c r="N184" t="n">
         <v>5855543</v>
       </c>
-      <c r="O184" t="n">
-        <v>792602834</v>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>792602834.0</t>
+        </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
@@ -13347,7 +13713,7 @@
     </row>
     <row r="185">
       <c r="A185" s="3" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -13406,8 +13772,10 @@
       <c r="N185" t="n">
         <v>5855544</v>
       </c>
-      <c r="O185" t="n">
-        <v>792602835</v>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>792602835.0</t>
+        </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
@@ -13476,8 +13844,10 @@
       <c r="N186" t="n">
         <v>5855545</v>
       </c>
-      <c r="O186" t="n">
-        <v>792602836</v>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>792602836.0</t>
+        </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
@@ -13546,8 +13916,10 @@
       <c r="N187" t="n">
         <v>5855546</v>
       </c>
-      <c r="O187" t="n">
-        <v>792602837</v>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>792602837.0</t>
+        </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
@@ -13557,7 +13929,7 @@
     </row>
     <row r="188">
       <c r="A188" s="3" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -13616,8 +13988,10 @@
       <c r="N188" t="n">
         <v>5855547</v>
       </c>
-      <c r="O188" t="n">
-        <v>792602838</v>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>792602838.0</t>
+        </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
@@ -13627,7 +14001,7 @@
     </row>
     <row r="189">
       <c r="A189" s="3" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -13686,8 +14060,10 @@
       <c r="N189" t="n">
         <v>5855548</v>
       </c>
-      <c r="O189" t="n">
-        <v>792602839</v>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>792602839.0</t>
+        </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
@@ -13697,7 +14073,7 @@
     </row>
     <row r="190">
       <c r="A190" s="3" t="n">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -13756,8 +14132,10 @@
       <c r="N190" t="n">
         <v>5855549</v>
       </c>
-      <c r="O190" t="n">
-        <v>792602840</v>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>792602840.0</t>
+        </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
@@ -13826,8 +14204,10 @@
       <c r="N191" t="n">
         <v>5855550</v>
       </c>
-      <c r="O191" t="n">
-        <v>792602841</v>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>792602841.0</t>
+        </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
@@ -13896,8 +14276,10 @@
       <c r="N192" t="n">
         <v>5634851</v>
       </c>
-      <c r="O192" t="n">
-        <v>792602842</v>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>792602842.0</t>
+        </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
@@ -13966,8 +14348,10 @@
       <c r="N193" t="n">
         <v>5634852</v>
       </c>
-      <c r="O193" t="n">
-        <v>792602843</v>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>792602843.0</t>
+        </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
@@ -14036,8 +14420,10 @@
       <c r="N194" t="n">
         <v>5634853</v>
       </c>
-      <c r="O194" t="n">
-        <v>792602844</v>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>792602844.0</t>
+        </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
@@ -14106,8 +14492,10 @@
       <c r="N195" t="n">
         <v>5634854</v>
       </c>
-      <c r="O195" t="n">
-        <v>792602845</v>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>792602845.0</t>
+        </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
@@ -14176,8 +14564,10 @@
       <c r="N196" t="n">
         <v>5634855</v>
       </c>
-      <c r="O196" t="n">
-        <v>792602846</v>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>792602846.0</t>
+        </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
@@ -14246,8 +14636,10 @@
       <c r="N197" t="n">
         <v>5634856</v>
       </c>
-      <c r="O197" t="n">
-        <v>792602847</v>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>792602847.0</t>
+        </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
@@ -14316,8 +14708,10 @@
       <c r="N198" t="n">
         <v>5634857</v>
       </c>
-      <c r="O198" t="n">
-        <v>792602848</v>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>792602848.0</t>
+        </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
@@ -14386,8 +14780,10 @@
       <c r="N199" t="n">
         <v>5634858</v>
       </c>
-      <c r="O199" t="n">
-        <v>792602849</v>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>792602849.0</t>
+        </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
@@ -14456,8 +14852,10 @@
       <c r="N200" t="n">
         <v>5634859</v>
       </c>
-      <c r="O200" t="n">
-        <v>792602850</v>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>792602850.0</t>
+        </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
@@ -14526,8 +14924,10 @@
       <c r="N201" t="n">
         <v>5634860</v>
       </c>
-      <c r="O201" t="n">
-        <v>792602851</v>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>792602851.0</t>
+        </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
@@ -14596,8 +14996,10 @@
       <c r="N202" t="n">
         <v>5634861</v>
       </c>
-      <c r="O202" t="n">
-        <v>792602852</v>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>792602852.0</t>
+        </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
@@ -14666,8 +15068,10 @@
       <c r="N203" t="n">
         <v>5634862</v>
       </c>
-      <c r="O203" t="n">
-        <v>792602853</v>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>792602853.0</t>
+        </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
@@ -14736,8 +15140,10 @@
       <c r="N204" t="n">
         <v>5634863</v>
       </c>
-      <c r="O204" t="n">
-        <v>792602854</v>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>792602854.0</t>
+        </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
@@ -14806,8 +15212,10 @@
       <c r="N205" t="n">
         <v>5634864</v>
       </c>
-      <c r="O205" t="n">
-        <v>792602855</v>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>792602855.0</t>
+        </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
@@ -14876,8 +15284,10 @@
       <c r="N206" t="n">
         <v>5634865</v>
       </c>
-      <c r="O206" t="n">
-        <v>792602856</v>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>792602856.0</t>
+        </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
@@ -14946,8 +15356,10 @@
       <c r="N207" t="n">
         <v>5634866</v>
       </c>
-      <c r="O207" t="n">
-        <v>792602857</v>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>792602857.0</t>
+        </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
@@ -15016,8 +15428,10 @@
       <c r="N208" t="n">
         <v>5634867</v>
       </c>
-      <c r="O208" t="n">
-        <v>792602858</v>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>792602858.0</t>
+        </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
@@ -15086,8 +15500,10 @@
       <c r="N209" t="n">
         <v>5634868</v>
       </c>
-      <c r="O209" t="n">
-        <v>792602859</v>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>792602859.0</t>
+        </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
@@ -15156,8 +15572,10 @@
       <c r="N210" t="n">
         <v>5634869</v>
       </c>
-      <c r="O210" t="n">
-        <v>792602860</v>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>792602860.0</t>
+        </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
@@ -15226,8 +15644,10 @@
       <c r="N211" t="n">
         <v>5634870</v>
       </c>
-      <c r="O211" t="n">
-        <v>792602861</v>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>792602861.0</t>
+        </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
@@ -15296,8 +15716,10 @@
       <c r="N212" t="n">
         <v>5634871</v>
       </c>
-      <c r="O212" t="n">
-        <v>792602862</v>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>792602862.0</t>
+        </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
@@ -15366,8 +15788,10 @@
       <c r="N213" t="n">
         <v>5634872</v>
       </c>
-      <c r="O213" t="n">
-        <v>792602863</v>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>792602863.0</t>
+        </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
@@ -15436,8 +15860,10 @@
       <c r="N214" t="n">
         <v>5634873</v>
       </c>
-      <c r="O214" t="n">
-        <v>792602864</v>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>792602864.0</t>
+        </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
@@ -15506,8 +15932,10 @@
       <c r="N215" t="n">
         <v>5634874</v>
       </c>
-      <c r="O215" t="n">
-        <v>792602865</v>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>792602865.0</t>
+        </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
@@ -15576,8 +16004,10 @@
       <c r="N216" t="n">
         <v>5634875</v>
       </c>
-      <c r="O216" t="n">
-        <v>792602866</v>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>792602866.0</t>
+        </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
@@ -15646,8 +16076,10 @@
       <c r="N217" t="n">
         <v>5634876</v>
       </c>
-      <c r="O217" t="n">
-        <v>792602867</v>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>792602867.0</t>
+        </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
@@ -15716,8 +16148,10 @@
       <c r="N218" t="n">
         <v>5634877</v>
       </c>
-      <c r="O218" t="n">
-        <v>792602868</v>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>792602868.0</t>
+        </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
@@ -15786,8 +16220,10 @@
       <c r="N219" t="n">
         <v>5634878</v>
       </c>
-      <c r="O219" t="n">
-        <v>792602869</v>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>792602869.0</t>
+        </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
@@ -15856,8 +16292,10 @@
       <c r="N220" t="n">
         <v>5634879</v>
       </c>
-      <c r="O220" t="n">
-        <v>792602870</v>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>792602870.0</t>
+        </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
@@ -15926,8 +16364,10 @@
       <c r="N221" t="n">
         <v>5634880</v>
       </c>
-      <c r="O221" t="n">
-        <v>792602871</v>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>792602871.0</t>
+        </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
@@ -15996,8 +16436,10 @@
       <c r="N222" t="n">
         <v>5634881</v>
       </c>
-      <c r="O222" t="n">
-        <v>792602872</v>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>792602872.0</t>
+        </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
@@ -16066,8 +16508,10 @@
       <c r="N223" t="n">
         <v>5634882</v>
       </c>
-      <c r="O223" t="n">
-        <v>792602873</v>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>792602873.0</t>
+        </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
@@ -16136,8 +16580,10 @@
       <c r="N224" t="n">
         <v>5634883</v>
       </c>
-      <c r="O224" t="n">
-        <v>792602874</v>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>792602874.0</t>
+        </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
@@ -16206,8 +16652,10 @@
       <c r="N225" t="n">
         <v>5634884</v>
       </c>
-      <c r="O225" t="n">
-        <v>792602875</v>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>792602875.0</t>
+        </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
@@ -16276,8 +16724,10 @@
       <c r="N226" t="n">
         <v>5634885</v>
       </c>
-      <c r="O226" t="n">
-        <v>792602876</v>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>792602876.0</t>
+        </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
@@ -16346,8 +16796,10 @@
       <c r="N227" t="n">
         <v>5634886</v>
       </c>
-      <c r="O227" t="n">
-        <v>792602877</v>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>792602877.0</t>
+        </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
@@ -16416,8 +16868,10 @@
       <c r="N228" t="n">
         <v>5634887</v>
       </c>
-      <c r="O228" t="n">
-        <v>792602878</v>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>792602878.0</t>
+        </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
@@ -16486,8 +16940,10 @@
       <c r="N229" t="n">
         <v>5634888</v>
       </c>
-      <c r="O229" t="n">
-        <v>792602879</v>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>792602879.0</t>
+        </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
@@ -16556,8 +17012,10 @@
       <c r="N230" t="n">
         <v>5634889</v>
       </c>
-      <c r="O230" t="n">
-        <v>792602880</v>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>792602880.0</t>
+        </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
@@ -16626,8 +17084,10 @@
       <c r="N231" t="n">
         <v>5634890</v>
       </c>
-      <c r="O231" t="n">
-        <v>792602881</v>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>792602881.0</t>
+        </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
@@ -16696,8 +17156,10 @@
       <c r="N232" t="n">
         <v>5634891</v>
       </c>
-      <c r="O232" t="n">
-        <v>792602882</v>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>792602882.0</t>
+        </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
@@ -16707,7 +17169,7 @@
     </row>
     <row r="233">
       <c r="A233" s="3" t="n">
-        <v>46113</v>
+        <v>46026</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -16766,8 +17228,10 @@
       <c r="N233" t="n">
         <v>5634892</v>
       </c>
-      <c r="O233" t="n">
-        <v>792602883</v>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>792602883.0</t>
+        </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
@@ -16836,8 +17300,10 @@
       <c r="N234" t="n">
         <v>5634893</v>
       </c>
-      <c r="O234" t="n">
-        <v>792602884</v>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>792602884.0</t>
+        </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
@@ -16906,8 +17372,10 @@
       <c r="N235" t="n">
         <v>5634894</v>
       </c>
-      <c r="O235" t="n">
-        <v>792602885</v>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>792602885.0</t>
+        </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
@@ -16976,8 +17444,10 @@
       <c r="N236" t="n">
         <v>5634895</v>
       </c>
-      <c r="O236" t="n">
-        <v>792602886</v>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>792602886.0</t>
+        </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
@@ -17046,8 +17516,10 @@
       <c r="N237" t="n">
         <v>5634896</v>
       </c>
-      <c r="O237" t="n">
-        <v>792602887</v>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>792602887.0</t>
+        </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
@@ -17116,8 +17588,10 @@
       <c r="N238" t="n">
         <v>5634897</v>
       </c>
-      <c r="O238" t="n">
-        <v>792602888</v>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>792602888.0</t>
+        </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
@@ -17186,8 +17660,10 @@
       <c r="N239" t="n">
         <v>5634898</v>
       </c>
-      <c r="O239" t="n">
-        <v>792602889</v>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>792602889.0</t>
+        </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
@@ -17197,7 +17673,7 @@
     </row>
     <row r="240">
       <c r="A240" s="3" t="n">
-        <v>46113</v>
+        <v>46026</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -17256,8 +17732,10 @@
       <c r="N240" t="n">
         <v>5634899</v>
       </c>
-      <c r="O240" t="n">
-        <v>792602890</v>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>792602890.0</t>
+        </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
@@ -17326,8 +17804,10 @@
       <c r="N241" t="n">
         <v>5634900</v>
       </c>
-      <c r="O241" t="n">
-        <v>792602891</v>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>792602891.0</t>
+        </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
@@ -17337,7 +17817,7 @@
     </row>
     <row r="242">
       <c r="A242" s="3" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -17396,8 +17876,10 @@
       <c r="N242" t="n">
         <v>5634901</v>
       </c>
-      <c r="O242" t="n">
-        <v>792602920</v>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>792602920.0</t>
+        </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
@@ -17407,7 +17889,7 @@
     </row>
     <row r="243">
       <c r="A243" s="3" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -17466,8 +17948,10 @@
       <c r="N243" t="n">
         <v>5634902</v>
       </c>
-      <c r="O243" t="n">
-        <v>792602921</v>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>792602921.0</t>
+        </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
@@ -17477,7 +17961,7 @@
     </row>
     <row r="244">
       <c r="A244" s="3" t="n">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -17536,8 +18020,10 @@
       <c r="N244" t="n">
         <v>5634903</v>
       </c>
-      <c r="O244" t="n">
-        <v>792602922</v>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>792602922.0</t>
+        </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
@@ -17547,7 +18033,7 @@
     </row>
     <row r="245">
       <c r="A245" s="3" t="n">
-        <v>46115</v>
+        <v>46085</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -17606,8 +18092,10 @@
       <c r="N245" t="n">
         <v>5634904</v>
       </c>
-      <c r="O245" t="n">
-        <v>792602923</v>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>792602923.0</t>
+        </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
@@ -17617,7 +18105,7 @@
     </row>
     <row r="246">
       <c r="A246" s="3" t="n">
-        <v>46119</v>
+        <v>46207</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -17676,8 +18164,10 @@
       <c r="N246" t="n">
         <v>5634905</v>
       </c>
-      <c r="O246" t="n">
-        <v>792602924</v>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>792602924.0</t>
+        </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
@@ -17687,7 +18177,7 @@
     </row>
     <row r="247">
       <c r="A247" s="3" t="n">
-        <v>46119</v>
+        <v>46207</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -17746,8 +18236,10 @@
       <c r="N247" t="n">
         <v>5634906</v>
       </c>
-      <c r="O247" t="n">
-        <v>792602925</v>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>792602925.0</t>
+        </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
@@ -17757,7 +18249,7 @@
     </row>
     <row r="248">
       <c r="A248" s="3" t="n">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -17816,8 +18308,10 @@
       <c r="N248" t="n">
         <v>5634907</v>
       </c>
-      <c r="O248" t="n">
-        <v>792602926</v>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>792602926.0</t>
+        </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
@@ -17827,7 +18321,7 @@
     </row>
     <row r="249">
       <c r="A249" s="3" t="n">
-        <v>46119</v>
+        <v>46207</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -17886,8 +18380,10 @@
       <c r="N249" t="n">
         <v>5634908</v>
       </c>
-      <c r="O249" t="n">
-        <v>792602927</v>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>792602927.0</t>
+        </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
@@ -17897,7 +18393,7 @@
     </row>
     <row r="250">
       <c r="A250" s="3" t="n">
-        <v>46119</v>
+        <v>46207</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -17956,8 +18452,10 @@
       <c r="N250" t="n">
         <v>5634909</v>
       </c>
-      <c r="O250" t="n">
-        <v>792602928</v>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>792602928.0</t>
+        </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
@@ -18026,8 +18524,10 @@
       <c r="N251" t="n">
         <v>5634910</v>
       </c>
-      <c r="O251" t="n">
-        <v>792602929</v>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>792602929.0</t>
+        </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
@@ -18037,7 +18537,7 @@
     </row>
     <row r="252">
       <c r="A252" s="3" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -18096,8 +18596,10 @@
       <c r="N252" t="n">
         <v>5634911</v>
       </c>
-      <c r="O252" t="n">
-        <v>792602930</v>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>792602930.0</t>
+        </is>
       </c>
       <c r="P252" t="inlineStr">
         <is>
@@ -18107,7 +18609,7 @@
     </row>
     <row r="253">
       <c r="A253" s="3" t="n">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -18166,8 +18668,10 @@
       <c r="N253" t="n">
         <v>5634912</v>
       </c>
-      <c r="O253" t="n">
-        <v>792602931</v>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>792602931.0</t>
+        </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
@@ -18177,7 +18681,7 @@
     </row>
     <row r="254">
       <c r="A254" s="3" t="n">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -18236,8 +18740,10 @@
       <c r="N254" t="n">
         <v>5634913</v>
       </c>
-      <c r="O254" t="n">
-        <v>792602932</v>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>792602932.0</t>
+        </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
@@ -18247,7 +18753,7 @@
     </row>
     <row r="255">
       <c r="A255" s="3" t="n">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -18306,8 +18812,10 @@
       <c r="N255" t="n">
         <v>5634914</v>
       </c>
-      <c r="O255" t="n">
-        <v>792602933</v>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>792602933.0</t>
+        </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
@@ -18317,7 +18825,7 @@
     </row>
     <row r="256">
       <c r="A256" s="3" t="n">
-        <v>46115</v>
+        <v>46085</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -18376,8 +18884,10 @@
       <c r="N256" t="n">
         <v>5634915</v>
       </c>
-      <c r="O256" t="n">
-        <v>792602934</v>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>792602934.0</t>
+        </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
@@ -18446,8 +18956,10 @@
       <c r="N257" t="n">
         <v>5634916</v>
       </c>
-      <c r="O257" t="n">
-        <v>792602935</v>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>792602935.0</t>
+        </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
@@ -18457,7 +18969,7 @@
     </row>
     <row r="258">
       <c r="A258" s="3" t="n">
-        <v>46120</v>
+        <v>46238</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -18516,8 +19028,10 @@
       <c r="N258" t="n">
         <v>5634917</v>
       </c>
-      <c r="O258" t="n">
-        <v>792602936</v>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>792602936.0</t>
+        </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
@@ -18527,7 +19041,7 @@
     </row>
     <row r="259">
       <c r="A259" s="3" t="n">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -18586,8 +19100,10 @@
       <c r="N259" t="n">
         <v>5634918</v>
       </c>
-      <c r="O259" t="n">
-        <v>792602937</v>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>792602937.0</t>
+        </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
@@ -18597,7 +19113,7 @@
     </row>
     <row r="260">
       <c r="A260" s="3" t="n">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -18656,8 +19172,10 @@
       <c r="N260" t="n">
         <v>5634919</v>
       </c>
-      <c r="O260" t="n">
-        <v>792602938</v>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>792602938.0</t>
+        </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
@@ -18667,7 +19185,7 @@
     </row>
     <row r="261">
       <c r="A261" s="3" t="n">
-        <v>46120</v>
+        <v>46238</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -18726,8 +19244,10 @@
       <c r="N261" t="n">
         <v>5634920</v>
       </c>
-      <c r="O261" t="n">
-        <v>792602939</v>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>792602939.0</t>
+        </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
@@ -18796,8 +19316,10 @@
       <c r="N262" t="n">
         <v>5634921</v>
       </c>
-      <c r="O262" t="n">
-        <v>792602940</v>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>792602940.0</t>
+        </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
@@ -18807,7 +19329,7 @@
     </row>
     <row r="263">
       <c r="A263" s="3" t="n">
-        <v>46120</v>
+        <v>46238</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -18866,8 +19388,10 @@
       <c r="N263" t="n">
         <v>5634922</v>
       </c>
-      <c r="O263" t="n">
-        <v>792602941</v>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>792602941.0</t>
+        </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
@@ -18877,7 +19401,7 @@
     </row>
     <row r="264">
       <c r="A264" s="3" t="n">
-        <v>46120</v>
+        <v>46238</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -18936,8 +19460,10 @@
       <c r="N264" t="n">
         <v>5634923</v>
       </c>
-      <c r="O264" t="n">
-        <v>792602942</v>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>792602942.0</t>
+        </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
@@ -18947,7 +19473,7 @@
     </row>
     <row r="265">
       <c r="A265" s="3" t="n">
-        <v>46118</v>
+        <v>46177</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -19006,8 +19532,10 @@
       <c r="N265" t="n">
         <v>5634924</v>
       </c>
-      <c r="O265" t="n">
-        <v>792602943</v>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>792602943.0</t>
+        </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
@@ -19017,7 +19545,7 @@
     </row>
     <row r="266">
       <c r="A266" s="3" t="n">
-        <v>46119</v>
+        <v>46207</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -19076,8 +19604,10 @@
       <c r="N266" t="n">
         <v>5634925</v>
       </c>
-      <c r="O266" t="n">
-        <v>792602944</v>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>792602944.0</t>
+        </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
@@ -19087,7 +19617,7 @@
     </row>
     <row r="267">
       <c r="A267" s="3" t="n">
-        <v>46119</v>
+        <v>46207</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -19146,8 +19676,10 @@
       <c r="N267" t="n">
         <v>5634926</v>
       </c>
-      <c r="O267" t="n">
-        <v>792602945</v>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>792602945.0</t>
+        </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
@@ -19157,7 +19689,7 @@
     </row>
     <row r="268">
       <c r="A268" s="3" t="n">
-        <v>46119</v>
+        <v>46207</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -19216,8 +19748,10 @@
       <c r="N268" t="n">
         <v>5634927</v>
       </c>
-      <c r="O268" t="n">
-        <v>792602946</v>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>792602946.0</t>
+        </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
@@ -19227,7 +19761,7 @@
     </row>
     <row r="269">
       <c r="A269" s="3" t="n">
-        <v>46119</v>
+        <v>46207</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -19286,8 +19820,10 @@
       <c r="N269" t="n">
         <v>5634928</v>
       </c>
-      <c r="O269" t="n">
-        <v>792602947</v>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>792602947.0</t>
+        </is>
       </c>
       <c r="P269" t="inlineStr">
         <is>
@@ -19297,7 +19833,7 @@
     </row>
     <row r="270">
       <c r="A270" s="3" t="n">
-        <v>46120</v>
+        <v>46238</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -19356,8 +19892,10 @@
       <c r="N270" t="n">
         <v>5634929</v>
       </c>
-      <c r="O270" t="n">
-        <v>792602948</v>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>792602948.0</t>
+        </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
@@ -19367,7 +19905,7 @@
     </row>
     <row r="271">
       <c r="A271" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -19426,8 +19964,10 @@
       <c r="N271" t="n">
         <v>5634930</v>
       </c>
-      <c r="O271" t="n">
-        <v>792602949</v>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>792602949.0</t>
+        </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
@@ -19437,7 +19977,7 @@
     </row>
     <row r="272">
       <c r="A272" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -19496,8 +20036,10 @@
       <c r="N272" t="n">
         <v>5634931</v>
       </c>
-      <c r="O272" t="n">
-        <v>792602950</v>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>792602950.0</t>
+        </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
@@ -19507,7 +20049,7 @@
     </row>
     <row r="273">
       <c r="A273" s="3" t="n">
-        <v>46120</v>
+        <v>46238</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -19566,8 +20108,10 @@
       <c r="N273" t="n">
         <v>5634932</v>
       </c>
-      <c r="O273" t="n">
-        <v>792602951</v>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>792602951.0</t>
+        </is>
       </c>
       <c r="P273" t="inlineStr">
         <is>
@@ -19577,7 +20121,7 @@
     </row>
     <row r="274">
       <c r="A274" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -19636,8 +20180,10 @@
       <c r="N274" t="n">
         <v>5634933</v>
       </c>
-      <c r="O274" t="n">
-        <v>792602952</v>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>792602952.0</t>
+        </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
@@ -19703,13 +20249,15 @@
       <c r="N275" t="n">
         <v>5634934</v>
       </c>
-      <c r="O275" t="n">
-        <v>792602953</v>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>792602953.0</t>
+        </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -19768,8 +20316,10 @@
       <c r="N276" t="n">
         <v>5634935</v>
       </c>
-      <c r="O276" t="n">
-        <v>792602954</v>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>792602954.0</t>
+        </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
@@ -19779,7 +20329,7 @@
     </row>
     <row r="277">
       <c r="A277" s="3" t="n">
-        <v>46120</v>
+        <v>46238</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -19838,8 +20388,10 @@
       <c r="N277" t="n">
         <v>5634936</v>
       </c>
-      <c r="O277" t="n">
-        <v>792602955</v>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>792602955.0</t>
+        </is>
       </c>
       <c r="P277" t="inlineStr">
         <is>
@@ -19849,7 +20401,7 @@
     </row>
     <row r="278">
       <c r="A278" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -19908,8 +20460,10 @@
       <c r="N278" t="n">
         <v>5634937</v>
       </c>
-      <c r="O278" t="n">
-        <v>792602956</v>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>792602956.0</t>
+        </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
@@ -19919,7 +20473,7 @@
     </row>
     <row r="279">
       <c r="A279" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -19978,8 +20532,10 @@
       <c r="N279" t="n">
         <v>5634938</v>
       </c>
-      <c r="O279" t="n">
-        <v>792602957</v>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>792602957.0</t>
+        </is>
       </c>
       <c r="P279" t="inlineStr">
         <is>
@@ -20048,8 +20604,10 @@
       <c r="N280" t="n">
         <v>5634939</v>
       </c>
-      <c r="O280" t="n">
-        <v>792602958</v>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>792602958.0</t>
+        </is>
       </c>
       <c r="P280" t="inlineStr">
         <is>
@@ -20059,7 +20617,7 @@
     </row>
     <row r="281">
       <c r="A281" s="3" t="n">
-        <v>46120</v>
+        <v>46238</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -20118,8 +20676,10 @@
       <c r="N281" t="n">
         <v>5634940</v>
       </c>
-      <c r="O281" t="n">
-        <v>792602959</v>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>792602959.0</t>
+        </is>
       </c>
       <c r="P281" t="inlineStr">
         <is>
@@ -20129,7 +20689,7 @@
     </row>
     <row r="282">
       <c r="A282" s="3" t="n">
-        <v>46122</v>
+        <v>46299</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -20188,8 +20748,10 @@
       <c r="N282" t="n">
         <v>5634941</v>
       </c>
-      <c r="O282" t="n">
-        <v>792602960</v>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>792602960.0</t>
+        </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
@@ -20199,7 +20761,7 @@
     </row>
     <row r="283">
       <c r="A283" s="3" t="n">
-        <v>46119</v>
+        <v>46207</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -20258,8 +20820,10 @@
       <c r="N283" t="n">
         <v>5634942</v>
       </c>
-      <c r="O283" t="n">
-        <v>792602961</v>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>792602961.0</t>
+        </is>
       </c>
       <c r="P283" t="inlineStr">
         <is>
@@ -20269,7 +20833,7 @@
     </row>
     <row r="284">
       <c r="A284" s="3" t="n">
-        <v>46119</v>
+        <v>46207</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -20328,8 +20892,10 @@
       <c r="N284" t="n">
         <v>5634943</v>
       </c>
-      <c r="O284" t="n">
-        <v>792602962</v>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>792602962.0</t>
+        </is>
       </c>
       <c r="P284" t="inlineStr">
         <is>
@@ -20339,7 +20905,7 @@
     </row>
     <row r="285">
       <c r="A285" s="3" t="n">
-        <v>46124</v>
+        <v>46360</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -20398,8 +20964,10 @@
       <c r="N285" t="n">
         <v>5634944</v>
       </c>
-      <c r="O285" t="n">
-        <v>792602963</v>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>792602963.0</t>
+        </is>
       </c>
       <c r="P285" t="inlineStr">
         <is>
@@ -20409,7 +20977,7 @@
     </row>
     <row r="286">
       <c r="A286" s="3" t="n">
-        <v>46123</v>
+        <v>46330</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -20468,8 +21036,10 @@
       <c r="N286" t="n">
         <v>5634945</v>
       </c>
-      <c r="O286" t="n">
-        <v>792602964</v>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>792602964.0</t>
+        </is>
       </c>
       <c r="P286" t="inlineStr">
         <is>
@@ -20479,7 +21049,7 @@
     </row>
     <row r="287">
       <c r="A287" s="3" t="n">
-        <v>46124</v>
+        <v>46360</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -20538,8 +21108,10 @@
       <c r="N287" t="n">
         <v>5634946</v>
       </c>
-      <c r="O287" t="n">
-        <v>792602965</v>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>792602965.0</t>
+        </is>
       </c>
       <c r="P287" t="inlineStr">
         <is>
@@ -20549,7 +21121,7 @@
     </row>
     <row r="288">
       <c r="A288" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -20608,8 +21180,10 @@
       <c r="N288" t="n">
         <v>5634947</v>
       </c>
-      <c r="O288" t="n">
-        <v>792602966</v>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>792602966.0</t>
+        </is>
       </c>
       <c r="P288" t="inlineStr">
         <is>
@@ -20619,7 +21193,7 @@
     </row>
     <row r="289">
       <c r="A289" s="3" t="n">
-        <v>46122</v>
+        <v>46299</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -20678,8 +21252,10 @@
       <c r="N289" t="n">
         <v>5634948</v>
       </c>
-      <c r="O289" t="n">
-        <v>792602967</v>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>792602967.0</t>
+        </is>
       </c>
       <c r="P289" t="inlineStr">
         <is>
@@ -20689,7 +21265,7 @@
     </row>
     <row r="290">
       <c r="A290" s="3" t="n">
-        <v>46124</v>
+        <v>46360</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -20748,8 +21324,10 @@
       <c r="N290" t="n">
         <v>5634949</v>
       </c>
-      <c r="O290" t="n">
-        <v>792602968</v>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>792602968.0</t>
+        </is>
       </c>
       <c r="P290" t="inlineStr">
         <is>
@@ -20759,7 +21337,7 @@
     </row>
     <row r="291">
       <c r="A291" s="3" t="n">
-        <v>46122</v>
+        <v>46299</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -20818,8 +21396,10 @@
       <c r="N291" t="n">
         <v>5634950</v>
       </c>
-      <c r="O291" t="n">
-        <v>792602969</v>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>792602969.0</t>
+        </is>
       </c>
       <c r="P291" t="inlineStr">
         <is>
@@ -20829,7 +21409,7 @@
     </row>
     <row r="292">
       <c r="A292" s="3" t="n">
-        <v>46119</v>
+        <v>46207</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -20888,8 +21468,10 @@
       <c r="N292" t="n">
         <v>5855701</v>
       </c>
-      <c r="O292" t="n">
-        <v>792602970</v>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>792602970.0</t>
+        </is>
       </c>
       <c r="P292" t="inlineStr">
         <is>
@@ -20899,7 +21481,7 @@
     </row>
     <row r="293">
       <c r="A293" s="3" t="n">
-        <v>46122</v>
+        <v>46299</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -20958,8 +21540,10 @@
       <c r="N293" t="n">
         <v>5855702</v>
       </c>
-      <c r="O293" t="n">
-        <v>792602971</v>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>792602971.0</t>
+        </is>
       </c>
       <c r="P293" t="inlineStr">
         <is>
@@ -20969,7 +21553,7 @@
     </row>
     <row r="294">
       <c r="A294" s="3" t="n">
-        <v>46123</v>
+        <v>46330</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -21028,8 +21612,10 @@
       <c r="N294" t="n">
         <v>5855703</v>
       </c>
-      <c r="O294" t="n">
-        <v>792602972</v>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>792602972.0</t>
+        </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
@@ -21039,7 +21625,7 @@
     </row>
     <row r="295">
       <c r="A295" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -21098,8 +21684,10 @@
       <c r="N295" t="n">
         <v>5855705</v>
       </c>
-      <c r="O295" t="n">
-        <v>792602973</v>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>792602973.0</t>
+        </is>
       </c>
       <c r="P295" t="inlineStr">
         <is>
@@ -21109,7 +21697,7 @@
     </row>
     <row r="296">
       <c r="A296" s="3" t="n">
-        <v>46122</v>
+        <v>46299</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -21168,8 +21756,10 @@
       <c r="N296" t="n">
         <v>5855706</v>
       </c>
-      <c r="O296" t="n">
-        <v>792602974</v>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>792602974.0</t>
+        </is>
       </c>
       <c r="P296" t="inlineStr">
         <is>
@@ -21179,7 +21769,7 @@
     </row>
     <row r="297">
       <c r="A297" s="3" t="n">
-        <v>46122</v>
+        <v>46299</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -21238,8 +21828,10 @@
       <c r="N297" t="n">
         <v>5855707</v>
       </c>
-      <c r="O297" t="n">
-        <v>792602975</v>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>792602975.0</t>
+        </is>
       </c>
       <c r="P297" t="inlineStr">
         <is>
@@ -21249,7 +21841,7 @@
     </row>
     <row r="298">
       <c r="A298" s="3" t="n">
-        <v>46122</v>
+        <v>46299</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -21308,8 +21900,10 @@
       <c r="N298" t="n">
         <v>5855708</v>
       </c>
-      <c r="O298" t="n">
-        <v>792602976</v>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>792602976.0</t>
+        </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
@@ -21319,7 +21913,7 @@
     </row>
     <row r="299">
       <c r="A299" s="3" t="n">
-        <v>46122</v>
+        <v>46299</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -21378,8 +21972,10 @@
       <c r="N299" t="n">
         <v>5855709</v>
       </c>
-      <c r="O299" t="n">
-        <v>792602977</v>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>792602977.0</t>
+        </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
@@ -21389,7 +21985,7 @@
     </row>
     <row r="300">
       <c r="A300" s="3" t="n">
-        <v>46122</v>
+        <v>46299</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -21448,8 +22044,10 @@
       <c r="N300" t="n">
         <v>5855710</v>
       </c>
-      <c r="O300" t="n">
-        <v>792602978</v>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>792602978.0</t>
+        </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
@@ -21459,7 +22057,7 @@
     </row>
     <row r="301">
       <c r="A301" s="3" t="n">
-        <v>46124</v>
+        <v>46360</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -21518,8 +22116,10 @@
       <c r="N301" t="n">
         <v>5855711</v>
       </c>
-      <c r="O301" t="n">
-        <v>792602979</v>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>792602979.0</t>
+        </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
@@ -21529,7 +22129,7 @@
     </row>
     <row r="302">
       <c r="A302" s="3" t="n">
-        <v>46122</v>
+        <v>46299</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -21588,8 +22188,10 @@
       <c r="N302" t="n">
         <v>5855712</v>
       </c>
-      <c r="O302" t="n">
-        <v>792602980</v>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>792602980.0</t>
+        </is>
       </c>
       <c r="P302" t="inlineStr">
         <is>
@@ -21599,7 +22201,7 @@
     </row>
     <row r="303">
       <c r="A303" s="3" t="n">
-        <v>46123</v>
+        <v>46330</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -21658,8 +22260,10 @@
       <c r="N303" t="n">
         <v>5855713</v>
       </c>
-      <c r="O303" t="n">
-        <v>792602981</v>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>792602981.0</t>
+        </is>
       </c>
       <c r="P303" t="inlineStr">
         <is>
@@ -21669,7 +22273,7 @@
     </row>
     <row r="304">
       <c r="A304" s="3" t="n">
-        <v>46122</v>
+        <v>46299</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -21728,8 +22332,10 @@
       <c r="N304" t="n">
         <v>5855714</v>
       </c>
-      <c r="O304" t="n">
-        <v>792602982</v>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>792602982.0</t>
+        </is>
       </c>
       <c r="P304" t="inlineStr">
         <is>
@@ -21739,7 +22345,7 @@
     </row>
     <row r="305">
       <c r="A305" s="3" t="n">
-        <v>46124</v>
+        <v>46360</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -21798,8 +22404,10 @@
       <c r="N305" t="n">
         <v>5855715</v>
       </c>
-      <c r="O305" t="n">
-        <v>792602983</v>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>792602983.0</t>
+        </is>
       </c>
       <c r="P305" t="inlineStr">
         <is>
@@ -21809,7 +22417,7 @@
     </row>
     <row r="306">
       <c r="A306" s="3" t="n">
-        <v>46124</v>
+        <v>46360</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
@@ -21868,8 +22476,10 @@
       <c r="N306" t="n">
         <v>5855716</v>
       </c>
-      <c r="O306" t="n">
-        <v>792602984</v>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>792602984.0</t>
+        </is>
       </c>
       <c r="P306" t="inlineStr">
         <is>
@@ -21938,8 +22548,10 @@
       <c r="N307" t="n">
         <v>5855717</v>
       </c>
-      <c r="O307" t="n">
-        <v>792602985</v>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>792602985.0</t>
+        </is>
       </c>
       <c r="P307" t="inlineStr">
         <is>
@@ -21949,7 +22561,7 @@
     </row>
     <row r="308">
       <c r="A308" s="3" t="n">
-        <v>46123</v>
+        <v>46330</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -22008,8 +22620,10 @@
       <c r="N308" t="n">
         <v>5855718</v>
       </c>
-      <c r="O308" t="n">
-        <v>792602986</v>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>792602986.0</t>
+        </is>
       </c>
       <c r="P308" t="inlineStr">
         <is>
@@ -22019,7 +22633,7 @@
     </row>
     <row r="309">
       <c r="A309" s="3" t="n">
-        <v>46124</v>
+        <v>46360</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -22078,8 +22692,10 @@
       <c r="N309" t="n">
         <v>5855719</v>
       </c>
-      <c r="O309" t="n">
-        <v>792602987</v>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>792602987.0</t>
+        </is>
       </c>
       <c r="P309" t="inlineStr">
         <is>
@@ -22148,8 +22764,10 @@
       <c r="N310" t="n">
         <v>5855720</v>
       </c>
-      <c r="O310" t="n">
-        <v>792602988</v>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>792602988.0</t>
+        </is>
       </c>
       <c r="P310" t="inlineStr">
         <is>
@@ -22159,7 +22777,7 @@
     </row>
     <row r="311">
       <c r="A311" s="3" t="n">
-        <v>46124</v>
+        <v>46360</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -22218,8 +22836,10 @@
       <c r="N311" t="n">
         <v>5855721</v>
       </c>
-      <c r="O311" t="n">
-        <v>792602989</v>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>792602989.0</t>
+        </is>
       </c>
       <c r="P311" t="inlineStr">
         <is>
@@ -22229,7 +22849,7 @@
     </row>
     <row r="312">
       <c r="A312" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -22288,8 +22908,10 @@
       <c r="N312" t="n">
         <v>5855722</v>
       </c>
-      <c r="O312" t="n">
-        <v>792602990</v>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>792602990.0</t>
+        </is>
       </c>
       <c r="P312" t="inlineStr">
         <is>
@@ -22358,8 +22980,10 @@
       <c r="N313" t="n">
         <v>5855723</v>
       </c>
-      <c r="O313" t="n">
-        <v>792602991</v>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>792602991.0</t>
+        </is>
       </c>
       <c r="P313" t="inlineStr">
         <is>
@@ -22369,7 +22993,7 @@
     </row>
     <row r="314">
       <c r="A314" s="3" t="n">
-        <v>46124</v>
+        <v>46360</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -22428,8 +23052,10 @@
       <c r="N314" t="n">
         <v>5855724</v>
       </c>
-      <c r="O314" t="n">
-        <v>792602992</v>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>792602992.0</t>
+        </is>
       </c>
       <c r="P314" t="inlineStr">
         <is>
@@ -22498,8 +23124,10 @@
       <c r="N315" t="n">
         <v>5855725</v>
       </c>
-      <c r="O315" t="n">
-        <v>792602993</v>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>792602993.0</t>
+        </is>
       </c>
       <c r="P315" t="inlineStr">
         <is>
@@ -22509,7 +23137,7 @@
     </row>
     <row r="316">
       <c r="A316" s="3" t="n">
-        <v>46123</v>
+        <v>46330</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -22568,8 +23196,10 @@
       <c r="N316" t="n">
         <v>5855726</v>
       </c>
-      <c r="O316" t="n">
-        <v>792602994</v>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>792602994.0</t>
+        </is>
       </c>
       <c r="P316" t="inlineStr">
         <is>
@@ -22579,7 +23209,7 @@
     </row>
     <row r="317">
       <c r="A317" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
@@ -22638,8 +23268,10 @@
       <c r="N317" t="n">
         <v>5855727</v>
       </c>
-      <c r="O317" t="n">
-        <v>792602995</v>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>792602995.0</t>
+        </is>
       </c>
       <c r="P317" t="inlineStr">
         <is>
@@ -22649,7 +23281,7 @@
     </row>
     <row r="318">
       <c r="A318" s="3" t="n">
-        <v>46124</v>
+        <v>46360</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -22708,8 +23340,10 @@
       <c r="N318" t="n">
         <v>5855728</v>
       </c>
-      <c r="O318" t="n">
-        <v>792602996</v>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>792602996.0</t>
+        </is>
       </c>
       <c r="P318" t="inlineStr">
         <is>
@@ -22719,7 +23353,7 @@
     </row>
     <row r="319">
       <c r="A319" s="3" t="n">
-        <v>46124</v>
+        <v>46360</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -22778,8 +23412,10 @@
       <c r="N319" t="n">
         <v>5855729</v>
       </c>
-      <c r="O319" t="n">
-        <v>792602997</v>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>792602997.0</t>
+        </is>
       </c>
       <c r="P319" t="inlineStr">
         <is>
@@ -22789,7 +23425,7 @@
     </row>
     <row r="320">
       <c r="A320" s="3" t="n">
-        <v>46124</v>
+        <v>46360</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -22848,8 +23484,10 @@
       <c r="N320" t="n">
         <v>5855730</v>
       </c>
-      <c r="O320" t="n">
-        <v>792602998</v>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>792602998.0</t>
+        </is>
       </c>
       <c r="P320" t="inlineStr">
         <is>
@@ -22918,8 +23556,10 @@
       <c r="N321" t="n">
         <v>5855731</v>
       </c>
-      <c r="O321" t="n">
-        <v>792602999</v>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>792602999.0</t>
+        </is>
       </c>
       <c r="P321" t="inlineStr">
         <is>
@@ -22929,7 +23569,7 @@
     </row>
     <row r="322">
       <c r="A322" s="3" t="n">
-        <v>46124</v>
+        <v>46360</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -22988,8 +23628,10 @@
       <c r="N322" t="n">
         <v>5855732</v>
       </c>
-      <c r="O322" t="n">
-        <v>792603000</v>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>792603000.0</t>
+        </is>
       </c>
       <c r="P322" t="inlineStr">
         <is>
@@ -23058,8 +23700,10 @@
       <c r="N323" t="n">
         <v>5855733</v>
       </c>
-      <c r="O323" t="n">
-        <v>792603001</v>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>792603001.0</t>
+        </is>
       </c>
       <c r="P323" t="inlineStr">
         <is>
@@ -23128,8 +23772,10 @@
       <c r="N324" t="n">
         <v>5855734</v>
       </c>
-      <c r="O324" t="n">
-        <v>792603002</v>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>792603002.0</t>
+        </is>
       </c>
       <c r="P324" t="inlineStr">
         <is>
@@ -23198,8 +23844,10 @@
       <c r="N325" t="n">
         <v>5855735</v>
       </c>
-      <c r="O325" t="n">
-        <v>792603003</v>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>792603003.0</t>
+        </is>
       </c>
       <c r="P325" t="inlineStr">
         <is>
@@ -23268,8 +23916,10 @@
       <c r="N326" t="n">
         <v>5855736</v>
       </c>
-      <c r="O326" t="n">
-        <v>792603004</v>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>792603004.0</t>
+        </is>
       </c>
       <c r="P326" t="inlineStr">
         <is>
@@ -23338,8 +23988,10 @@
       <c r="N327" t="n">
         <v>5855737</v>
       </c>
-      <c r="O327" t="n">
-        <v>792603005</v>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>792603005.0</t>
+        </is>
       </c>
       <c r="P327" t="inlineStr">
         <is>
@@ -23408,8 +24060,10 @@
       <c r="N328" t="n">
         <v>5855738</v>
       </c>
-      <c r="O328" t="n">
-        <v>792603006</v>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>792603006.0</t>
+        </is>
       </c>
       <c r="P328" t="inlineStr">
         <is>
@@ -23478,8 +24132,10 @@
       <c r="N329" t="n">
         <v>5855739</v>
       </c>
-      <c r="O329" t="n">
-        <v>792603007</v>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>792603007.0</t>
+        </is>
       </c>
       <c r="P329" t="inlineStr">
         <is>
@@ -23489,7 +24145,7 @@
     </row>
     <row r="330">
       <c r="A330" s="3" t="n">
-        <v>46122</v>
+        <v>46299</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -23548,8 +24204,10 @@
       <c r="N330" t="n">
         <v>5855740</v>
       </c>
-      <c r="O330" t="n">
-        <v>792603008</v>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>792603008.0</t>
+        </is>
       </c>
       <c r="P330" t="inlineStr">
         <is>
@@ -23618,8 +24276,10 @@
       <c r="N331" t="n">
         <v>5855741</v>
       </c>
-      <c r="O331" t="n">
-        <v>792603009</v>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>792603009.0</t>
+        </is>
       </c>
       <c r="P331" t="inlineStr">
         <is>
@@ -23688,8 +24348,10 @@
       <c r="N332" t="n">
         <v>5855742</v>
       </c>
-      <c r="O332" t="n">
-        <v>792603010</v>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>792603010.0</t>
+        </is>
       </c>
       <c r="P332" t="inlineStr">
         <is>
@@ -23758,8 +24420,10 @@
       <c r="N333" t="n">
         <v>5855743</v>
       </c>
-      <c r="O333" t="n">
-        <v>792603011</v>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>792603011.0</t>
+        </is>
       </c>
       <c r="P333" t="inlineStr">
         <is>
@@ -23769,7 +24433,7 @@
     </row>
     <row r="334">
       <c r="A334" s="3" t="n">
-        <v>46123</v>
+        <v>46330</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
@@ -23828,8 +24492,10 @@
       <c r="N334" t="n">
         <v>5855744</v>
       </c>
-      <c r="O334" t="n">
-        <v>792603012</v>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>792603012.0</t>
+        </is>
       </c>
       <c r="P334" t="inlineStr">
         <is>
@@ -23898,8 +24564,10 @@
       <c r="N335" t="n">
         <v>5855745</v>
       </c>
-      <c r="O335" t="n">
-        <v>792603013</v>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>792603013.0</t>
+        </is>
       </c>
       <c r="P335" t="inlineStr">
         <is>
@@ -23968,8 +24636,10 @@
       <c r="N336" t="n">
         <v>5855746</v>
       </c>
-      <c r="O336" t="n">
-        <v>792603014</v>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>792603014.0</t>
+        </is>
       </c>
       <c r="P336" t="inlineStr">
         <is>
@@ -24038,8 +24708,10 @@
       <c r="N337" t="n">
         <v>5855747</v>
       </c>
-      <c r="O337" t="n">
-        <v>792603015</v>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>792603015.0</t>
+        </is>
       </c>
       <c r="P337" t="inlineStr">
         <is>
@@ -24049,7 +24721,7 @@
     </row>
     <row r="338">
       <c r="A338" s="3" t="n">
-        <v>46123</v>
+        <v>46330</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
@@ -24108,8 +24780,10 @@
       <c r="N338" t="n">
         <v>5855748</v>
       </c>
-      <c r="O338" t="n">
-        <v>792603016</v>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>792603016.0</t>
+        </is>
       </c>
       <c r="P338" t="inlineStr">
         <is>
@@ -24178,8 +24852,10 @@
       <c r="N339" t="n">
         <v>5855749</v>
       </c>
-      <c r="O339" t="n">
-        <v>792603017</v>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>792603017.0</t>
+        </is>
       </c>
       <c r="P339" t="inlineStr">
         <is>
@@ -24248,8 +24924,10 @@
       <c r="N340" t="n">
         <v>5855750</v>
       </c>
-      <c r="O340" t="n">
-        <v>792603018</v>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>792603018.0</t>
+        </is>
       </c>
       <c r="P340" t="inlineStr">
         <is>
@@ -24318,8 +24996,10 @@
       <c r="N341" t="n">
         <v>5634651</v>
       </c>
-      <c r="O341" t="n">
-        <v>792603019</v>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>792603019.0</t>
+        </is>
       </c>
       <c r="P341" t="inlineStr">
         <is>
@@ -24388,8 +25068,10 @@
       <c r="N342" t="n">
         <v>6662232</v>
       </c>
-      <c r="O342" t="n">
-        <v>792603046</v>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>792603046.0</t>
+        </is>
       </c>
       <c r="P342" t="inlineStr">
         <is>
@@ -24458,8 +25140,10 @@
       <c r="N343" t="n">
         <v>6662233</v>
       </c>
-      <c r="O343" t="n">
-        <v>792603047</v>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>792603047.0</t>
+        </is>
       </c>
       <c r="P343" t="inlineStr">
         <is>
@@ -24469,7 +25153,7 @@
     </row>
     <row r="344">
       <c r="A344" s="3" t="n">
-        <v>46082</v>
+        <v>46025</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
@@ -24528,8 +25212,10 @@
       <c r="N344" t="n">
         <v>6662234</v>
       </c>
-      <c r="O344" t="n">
-        <v>792603048</v>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>792603048.0</t>
+        </is>
       </c>
       <c r="P344" t="inlineStr">
         <is>
@@ -24539,7 +25225,7 @@
     </row>
     <row r="345">
       <c r="A345" s="3" t="n">
-        <v>46083</v>
+        <v>46056</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
@@ -24598,8 +25284,10 @@
       <c r="N345" t="n">
         <v>6662235</v>
       </c>
-      <c r="O345" t="n">
-        <v>792603049</v>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>792603049.0</t>
+        </is>
       </c>
       <c r="P345" t="inlineStr">
         <is>
@@ -24609,7 +25297,7 @@
     </row>
     <row r="346">
       <c r="A346" s="3" t="n">
-        <v>46087</v>
+        <v>46176</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
@@ -24668,8 +25356,10 @@
       <c r="N346" t="n">
         <v>6662236</v>
       </c>
-      <c r="O346" t="n">
-        <v>792603050</v>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>792603050.0</t>
+        </is>
       </c>
       <c r="P346" t="inlineStr">
         <is>
@@ -24679,7 +25369,7 @@
     </row>
     <row r="347">
       <c r="A347" s="3" t="n">
-        <v>46093</v>
+        <v>46359</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
@@ -24738,8 +25428,10 @@
       <c r="N347" t="n">
         <v>6662237</v>
       </c>
-      <c r="O347" t="n">
-        <v>792603051</v>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>792603051.0</t>
+        </is>
       </c>
       <c r="P347" t="inlineStr">
         <is>
@@ -24808,8 +25500,10 @@
       <c r="N348" t="n">
         <v>6662238</v>
       </c>
-      <c r="O348" t="n">
-        <v>792603052</v>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>792603052.0</t>
+        </is>
       </c>
       <c r="P348" t="inlineStr">
         <is>
@@ -24878,8 +25572,10 @@
       <c r="N349" t="n">
         <v>6662239</v>
       </c>
-      <c r="O349" t="n">
-        <v>792603053</v>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>792603053.0</t>
+        </is>
       </c>
       <c r="P349" t="inlineStr">
         <is>
@@ -24948,8 +25644,10 @@
       <c r="N350" t="n">
         <v>6662240</v>
       </c>
-      <c r="O350" t="n">
-        <v>792603054</v>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>792603054.0</t>
+        </is>
       </c>
       <c r="P350" t="inlineStr">
         <is>
@@ -25018,8 +25716,10 @@
       <c r="N351" t="n">
         <v>6662241</v>
       </c>
-      <c r="O351" t="n">
-        <v>792603055</v>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>792603055.0</t>
+        </is>
       </c>
       <c r="P351" t="inlineStr">
         <is>
@@ -25088,8 +25788,10 @@
       <c r="N352" t="n">
         <v>6662242</v>
       </c>
-      <c r="O352" t="n">
-        <v>792603056</v>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>792603056.0</t>
+        </is>
       </c>
       <c r="P352" t="inlineStr">
         <is>
@@ -25158,8 +25860,10 @@
       <c r="N353" t="n">
         <v>6662243</v>
       </c>
-      <c r="O353" t="n">
-        <v>792603057</v>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>792603057.0</t>
+        </is>
       </c>
       <c r="P353" t="inlineStr">
         <is>
@@ -25228,8 +25932,10 @@
       <c r="N354" t="n">
         <v>6662244</v>
       </c>
-      <c r="O354" t="n">
-        <v>792603058</v>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>792603058.0</t>
+        </is>
       </c>
       <c r="P354" t="inlineStr">
         <is>
@@ -25298,8 +26004,10 @@
       <c r="N355" t="n">
         <v>6662245</v>
       </c>
-      <c r="O355" t="n">
-        <v>792603059</v>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>792603059.0</t>
+        </is>
       </c>
       <c r="P355" t="inlineStr">
         <is>
@@ -25368,8 +26076,10 @@
       <c r="N356" t="n">
         <v>6662246</v>
       </c>
-      <c r="O356" t="n">
-        <v>792603060</v>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>792603060.0</t>
+        </is>
       </c>
       <c r="P356" t="inlineStr">
         <is>
@@ -25379,7 +26089,7 @@
     </row>
     <row r="357">
       <c r="A357" s="3" t="n">
-        <v>46119</v>
+        <v>46207</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -25438,8 +26148,10 @@
       <c r="N357" t="n">
         <v>6662247</v>
       </c>
-      <c r="O357" t="n">
-        <v>792603061</v>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>792603061.0</t>
+        </is>
       </c>
       <c r="P357" t="inlineStr">
         <is>
@@ -25449,7 +26161,7 @@
     </row>
     <row r="358">
       <c r="A358" s="3" t="n">
-        <v>46122</v>
+        <v>46299</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -25508,8 +26220,10 @@
       <c r="N358" t="n">
         <v>6662248</v>
       </c>
-      <c r="O358" t="n">
-        <v>792603062</v>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>792603062.0</t>
+        </is>
       </c>
       <c r="P358" t="inlineStr">
         <is>
@@ -25519,7 +26233,7 @@
     </row>
     <row r="359">
       <c r="A359" s="3" t="n">
-        <v>46123</v>
+        <v>46330</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -25578,8 +26292,10 @@
       <c r="N359" t="n">
         <v>6662249</v>
       </c>
-      <c r="O359" t="n">
-        <v>792603063</v>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>792603063.0</t>
+        </is>
       </c>
       <c r="P359" t="inlineStr">
         <is>
@@ -25648,8 +26364,10 @@
       <c r="N360" t="n">
         <v>6662250</v>
       </c>
-      <c r="O360" t="n">
-        <v>792603064</v>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>792603064.0</t>
+        </is>
       </c>
       <c r="P360" t="inlineStr">
         <is>
@@ -25659,7 +26377,7 @@
     </row>
     <row r="361">
       <c r="A361" s="3" t="n">
-        <v>46085</v>
+        <v>46115</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
@@ -25718,8 +26436,10 @@
       <c r="N361" t="n">
         <v>6741762</v>
       </c>
-      <c r="O361" t="n">
-        <v>792603065</v>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>792603065.0</t>
+        </is>
       </c>
       <c r="P361" t="inlineStr">
         <is>
@@ -25729,7 +26449,7 @@
     </row>
     <row r="362">
       <c r="A362" s="3" t="n">
-        <v>46086</v>
+        <v>46145</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -25788,8 +26508,10 @@
       <c r="N362" t="n">
         <v>6741763</v>
       </c>
-      <c r="O362" t="n">
-        <v>792603066</v>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>792603066.0</t>
+        </is>
       </c>
       <c r="P362" t="inlineStr">
         <is>
@@ -25799,7 +26521,7 @@
     </row>
     <row r="363">
       <c r="A363" s="3" t="n">
-        <v>46087</v>
+        <v>46176</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
@@ -25858,8 +26580,10 @@
       <c r="N363" t="n">
         <v>6741764</v>
       </c>
-      <c r="O363" t="n">
-        <v>792603067</v>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>792603067.0</t>
+        </is>
       </c>
       <c r="P363" t="inlineStr">
         <is>
@@ -25869,7 +26593,7 @@
     </row>
     <row r="364">
       <c r="A364" s="3" t="n">
-        <v>46088</v>
+        <v>46206</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -25928,8 +26652,10 @@
       <c r="N364" t="n">
         <v>6741765</v>
       </c>
-      <c r="O364" t="n">
-        <v>792603068</v>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>792603068.0</t>
+        </is>
       </c>
       <c r="P364" t="inlineStr">
         <is>
@@ -25939,7 +26665,7 @@
     </row>
     <row r="365">
       <c r="A365" s="3" t="n">
-        <v>46088</v>
+        <v>46206</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
@@ -25998,8 +26724,10 @@
       <c r="N365" t="n">
         <v>6741766</v>
       </c>
-      <c r="O365" t="n">
-        <v>792603069</v>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>792603069.0</t>
+        </is>
       </c>
       <c r="P365" t="inlineStr">
         <is>
@@ -26009,7 +26737,7 @@
     </row>
     <row r="366">
       <c r="A366" s="3" t="n">
-        <v>46088</v>
+        <v>46206</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
@@ -26068,8 +26796,10 @@
       <c r="N366" t="n">
         <v>6741767</v>
       </c>
-      <c r="O366" t="n">
-        <v>792603070</v>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>792603070.0</t>
+        </is>
       </c>
       <c r="P366" t="inlineStr">
         <is>
@@ -26079,7 +26809,7 @@
     </row>
     <row r="367">
       <c r="A367" s="3" t="n">
-        <v>46088</v>
+        <v>46206</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
@@ -26138,8 +26868,10 @@
       <c r="N367" t="n">
         <v>6741768</v>
       </c>
-      <c r="O367" t="n">
-        <v>792603071</v>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>792603071.0</t>
+        </is>
       </c>
       <c r="P367" t="inlineStr">
         <is>
@@ -26149,7 +26881,7 @@
     </row>
     <row r="368">
       <c r="A368" s="3" t="n">
-        <v>46090</v>
+        <v>46268</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
@@ -26208,8 +26940,10 @@
       <c r="N368" t="n">
         <v>6741769</v>
       </c>
-      <c r="O368" t="n">
-        <v>792603072</v>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>792603072.0</t>
+        </is>
       </c>
       <c r="P368" t="inlineStr">
         <is>
@@ -26219,7 +26953,7 @@
     </row>
     <row r="369">
       <c r="A369" s="3" t="n">
-        <v>46093</v>
+        <v>46359</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
@@ -26278,8 +27012,10 @@
       <c r="N369" t="n">
         <v>6741770</v>
       </c>
-      <c r="O369" t="n">
-        <v>792603073</v>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>792603073.0</t>
+        </is>
       </c>
       <c r="P369" t="inlineStr">
         <is>
@@ -26289,7 +27025,7 @@
     </row>
     <row r="370">
       <c r="A370" s="3" t="n">
-        <v>46092</v>
+        <v>46329</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -26348,8 +27084,10 @@
       <c r="N370" t="n">
         <v>6741771</v>
       </c>
-      <c r="O370" t="n">
-        <v>792603074</v>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>792603074.0</t>
+        </is>
       </c>
       <c r="P370" t="inlineStr">
         <is>
@@ -26359,7 +27097,7 @@
     </row>
     <row r="371">
       <c r="A371" s="3" t="n">
-        <v>46092</v>
+        <v>46329</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -26418,8 +27156,10 @@
       <c r="N371" t="n">
         <v>6741772</v>
       </c>
-      <c r="O371" t="n">
-        <v>792603075</v>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>792603075.0</t>
+        </is>
       </c>
       <c r="P371" t="inlineStr">
         <is>
@@ -26429,7 +27169,7 @@
     </row>
     <row r="372">
       <c r="A372" s="3" t="n">
-        <v>46092</v>
+        <v>46329</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -26488,8 +27228,10 @@
       <c r="N372" t="n">
         <v>6741773</v>
       </c>
-      <c r="O372" t="n">
-        <v>792603076</v>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>792603076.0</t>
+        </is>
       </c>
       <c r="P372" t="inlineStr">
         <is>
@@ -26499,7 +27241,7 @@
     </row>
     <row r="373">
       <c r="A373" s="3" t="n">
-        <v>46093</v>
+        <v>46359</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
@@ -26558,8 +27300,10 @@
       <c r="N373" t="n">
         <v>6741774</v>
       </c>
-      <c r="O373" t="n">
-        <v>792603077</v>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>792603077.0</t>
+        </is>
       </c>
       <c r="P373" t="inlineStr">
         <is>
@@ -26569,7 +27313,7 @@
     </row>
     <row r="374">
       <c r="A374" s="3" t="n">
-        <v>46093</v>
+        <v>46359</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
@@ -26628,8 +27372,10 @@
       <c r="N374" t="n">
         <v>6741775</v>
       </c>
-      <c r="O374" t="n">
-        <v>792603078</v>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>792603078.0</t>
+        </is>
       </c>
       <c r="P374" t="inlineStr">
         <is>
@@ -26698,8 +27444,10 @@
       <c r="N375" t="n">
         <v>6741776</v>
       </c>
-      <c r="O375" t="n">
-        <v>792603079</v>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>792603079.0</t>
+        </is>
       </c>
       <c r="P375" t="inlineStr">
         <is>
@@ -26768,8 +27516,10 @@
       <c r="N376" t="n">
         <v>6741777</v>
       </c>
-      <c r="O376" t="n">
-        <v>792603080</v>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>792603080.0</t>
+        </is>
       </c>
       <c r="P376" t="inlineStr">
         <is>
@@ -26838,8 +27588,10 @@
       <c r="N377" t="n">
         <v>6741779</v>
       </c>
-      <c r="O377" t="n">
-        <v>792603081</v>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>792603081.0</t>
+        </is>
       </c>
       <c r="P377" t="inlineStr">
         <is>
@@ -26908,8 +27660,10 @@
       <c r="N378" t="n">
         <v>6741780</v>
       </c>
-      <c r="O378" t="n">
-        <v>792603082</v>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>792603082.0</t>
+        </is>
       </c>
       <c r="P378" t="inlineStr">
         <is>
@@ -26978,8 +27732,10 @@
       <c r="N379" t="n">
         <v>6741781</v>
       </c>
-      <c r="O379" t="n">
-        <v>792603083</v>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>792603083.0</t>
+        </is>
       </c>
       <c r="P379" t="inlineStr">
         <is>
@@ -27048,8 +27804,10 @@
       <c r="N380" t="n">
         <v>6741782</v>
       </c>
-      <c r="O380" t="n">
-        <v>792603084</v>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>792603084.0</t>
+        </is>
       </c>
       <c r="P380" t="inlineStr">
         <is>
@@ -27118,8 +27876,10 @@
       <c r="N381" t="n">
         <v>6741783</v>
       </c>
-      <c r="O381" t="n">
-        <v>792603085</v>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>792603085.0</t>
+        </is>
       </c>
       <c r="P381" t="inlineStr">
         <is>
@@ -27188,8 +27948,10 @@
       <c r="N382" t="n">
         <v>6741784</v>
       </c>
-      <c r="O382" t="n">
-        <v>792603086</v>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>792603086.0</t>
+        </is>
       </c>
       <c r="P382" t="inlineStr">
         <is>
@@ -27258,8 +28020,10 @@
       <c r="N383" t="n">
         <v>6741785</v>
       </c>
-      <c r="O383" t="n">
-        <v>792603087</v>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>792603087.0</t>
+        </is>
       </c>
       <c r="P383" t="inlineStr">
         <is>
@@ -27328,8 +28092,10 @@
       <c r="N384" t="n">
         <v>6741786</v>
       </c>
-      <c r="O384" t="n">
-        <v>792603088</v>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>792603088.0</t>
+        </is>
       </c>
       <c r="P384" t="inlineStr">
         <is>
@@ -27398,8 +28164,10 @@
       <c r="N385" t="n">
         <v>6741787</v>
       </c>
-      <c r="O385" t="n">
-        <v>792603089</v>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>792603089.0</t>
+        </is>
       </c>
       <c r="P385" t="inlineStr">
         <is>
@@ -27468,8 +28236,10 @@
       <c r="N386" t="n">
         <v>6741788</v>
       </c>
-      <c r="O386" t="n">
-        <v>792603090</v>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>792603090.0</t>
+        </is>
       </c>
       <c r="P386" t="inlineStr">
         <is>
@@ -27538,8 +28308,10 @@
       <c r="N387" t="n">
         <v>6741789</v>
       </c>
-      <c r="O387" t="n">
-        <v>792603091</v>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>792603091.0</t>
+        </is>
       </c>
       <c r="P387" t="inlineStr">
         <is>
@@ -27608,8 +28380,10 @@
       <c r="N388" t="n">
         <v>6741790</v>
       </c>
-      <c r="O388" t="n">
-        <v>792603092</v>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>792603092.0</t>
+        </is>
       </c>
       <c r="P388" t="inlineStr">
         <is>
@@ -27678,8 +28452,10 @@
       <c r="N389" t="n">
         <v>6741791</v>
       </c>
-      <c r="O389" t="n">
-        <v>792603093</v>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>792603093.0</t>
+        </is>
       </c>
       <c r="P389" t="inlineStr">
         <is>
@@ -27748,8 +28524,10 @@
       <c r="N390" t="n">
         <v>6741793</v>
       </c>
-      <c r="O390" t="n">
-        <v>792603094</v>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>792603094.0</t>
+        </is>
       </c>
       <c r="P390" t="inlineStr">
         <is>
@@ -27818,8 +28596,10 @@
       <c r="N391" t="n">
         <v>6741794</v>
       </c>
-      <c r="O391" t="n">
-        <v>792603095</v>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>792603095.0</t>
+        </is>
       </c>
       <c r="P391" t="inlineStr">
         <is>
@@ -27888,8 +28668,10 @@
       <c r="N392" t="n">
         <v>6741795</v>
       </c>
-      <c r="O392" t="n">
-        <v>792603096</v>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>792603096.0</t>
+        </is>
       </c>
       <c r="P392" t="inlineStr">
         <is>
@@ -27958,8 +28740,10 @@
       <c r="N393" t="n">
         <v>6741796</v>
       </c>
-      <c r="O393" t="n">
-        <v>792603097</v>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>792603097.0</t>
+        </is>
       </c>
       <c r="P393" t="inlineStr">
         <is>
@@ -28028,8 +28812,10 @@
       <c r="N394" t="n">
         <v>6741797</v>
       </c>
-      <c r="O394" t="n">
-        <v>792603098</v>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>792603098.0</t>
+        </is>
       </c>
       <c r="P394" t="inlineStr">
         <is>
@@ -28098,8 +28884,10 @@
       <c r="N395" t="n">
         <v>6741798</v>
       </c>
-      <c r="O395" t="n">
-        <v>792603099</v>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>792603099.0</t>
+        </is>
       </c>
       <c r="P395" t="inlineStr">
         <is>
@@ -28168,8 +28956,10 @@
       <c r="N396" t="n">
         <v>6741799</v>
       </c>
-      <c r="O396" t="n">
-        <v>792603100</v>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>792603100.0</t>
+        </is>
       </c>
       <c r="P396" t="inlineStr">
         <is>
@@ -28238,8 +29028,10 @@
       <c r="N397" t="n">
         <v>5550501</v>
       </c>
-      <c r="O397" t="n">
-        <v>792603101</v>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>792603101.0</t>
+        </is>
       </c>
       <c r="P397" t="inlineStr">
         <is>
@@ -28308,8 +29100,10 @@
       <c r="N398" t="n">
         <v>5550502</v>
       </c>
-      <c r="O398" t="n">
-        <v>792603102</v>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>792603102.0</t>
+        </is>
       </c>
       <c r="P398" t="inlineStr">
         <is>
@@ -28319,7 +29113,7 @@
     </row>
     <row r="399">
       <c r="A399" s="3" t="n">
-        <v>46119</v>
+        <v>46207</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -28378,8 +29172,10 @@
       <c r="N399" t="n">
         <v>5550503</v>
       </c>
-      <c r="O399" t="n">
-        <v>792603103</v>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>792603103.0</t>
+        </is>
       </c>
       <c r="P399" t="inlineStr">
         <is>
@@ -28389,7 +29185,7 @@
     </row>
     <row r="400">
       <c r="A400" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -28448,8 +29244,10 @@
       <c r="N400" t="n">
         <v>5550504</v>
       </c>
-      <c r="O400" t="n">
-        <v>792603104</v>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>792603104.0</t>
+        </is>
       </c>
       <c r="P400" t="inlineStr">
         <is>
@@ -28459,7 +29257,7 @@
     </row>
     <row r="401">
       <c r="A401" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -28518,8 +29316,10 @@
       <c r="N401" t="n">
         <v>5550505</v>
       </c>
-      <c r="O401" t="n">
-        <v>792603105</v>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>792603105.0</t>
+        </is>
       </c>
       <c r="P401" t="inlineStr">
         <is>
@@ -28529,7 +29329,7 @@
     </row>
     <row r="402">
       <c r="A402" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -28588,8 +29388,10 @@
       <c r="N402" t="n">
         <v>5550506</v>
       </c>
-      <c r="O402" t="n">
-        <v>792603106</v>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>792603106.0</t>
+        </is>
       </c>
       <c r="P402" t="inlineStr">
         <is>
@@ -28599,7 +29401,7 @@
     </row>
     <row r="403">
       <c r="A403" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -28658,8 +29460,10 @@
       <c r="N403" t="n">
         <v>5550507</v>
       </c>
-      <c r="O403" t="n">
-        <v>792603107</v>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>792603107.0</t>
+        </is>
       </c>
       <c r="P403" t="inlineStr">
         <is>
@@ -28669,7 +29473,7 @@
     </row>
     <row r="404">
       <c r="A404" s="3" t="n">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
@@ -28728,8 +29532,10 @@
       <c r="N404" t="n">
         <v>5550508</v>
       </c>
-      <c r="O404" t="n">
-        <v>792603108</v>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>792603108.0</t>
+        </is>
       </c>
       <c r="P404" t="inlineStr">
         <is>
@@ -28798,8 +29604,10 @@
       <c r="N405" t="n">
         <v>5550509</v>
       </c>
-      <c r="O405" t="n">
-        <v>792603109</v>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>792603109.0</t>
+        </is>
       </c>
       <c r="P405" t="inlineStr">
         <is>
@@ -28868,8 +29676,10 @@
       <c r="N406" t="n">
         <v>5550510</v>
       </c>
-      <c r="O406" t="n">
-        <v>792603110</v>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>792603110.0</t>
+        </is>
       </c>
       <c r="P406" t="inlineStr">
         <is>
